--- a/04_Yetkili_Kullanıcı_Profile_Settings/4 - AU - PS.xlsx
+++ b/04_Yetkili_Kullanıcı_Profile_Settings/4 - AU - PS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bovay\Desktop\¨¨¨¨¨¨\PROJECTS\CV TASLAK\POWER PULSE - PROJE\PLANLAMA\04 - YETKİLİ KULLANICI - PROFİL AYARLARI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8137525C-4318-4B56-868A-93F2CE14D837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2869CDED-F9B7-45FA-BD1C-72F5A701652F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="12090" firstSheet="9" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4. GEREKSİNİM TAKİP MATRİSİ" sheetId="11" r:id="rId1"/>
@@ -1899,6 +1899,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2087,18 +2099,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2490,21 +2490,21 @@
       <c r="A1" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="77" t="s">
         <v>241</v>
       </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
       <c r="H1" s="58"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="79" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="74"/>
+      <c r="C2" s="78"/>
       <c r="F2" s="59" t="s">
         <v>138</v>
       </c>
@@ -2517,11 +2517,11 @@
       <c r="A3" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="79" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
       <c r="F3" s="59" t="s">
         <v>140</v>
       </c>
@@ -2534,10 +2534,10 @@
       <c r="A4" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="76" t="s">
+      <c r="B4" s="80" t="s">
         <v>154</v>
       </c>
-      <c r="C4" s="76"/>
+      <c r="C4" s="80"/>
       <c r="F4" s="57" t="s">
         <v>142</v>
       </c>
@@ -2577,7 +2577,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="155" t="s">
+      <c r="A8" s="73" t="s">
         <v>157</v>
       </c>
       <c r="B8" s="64" t="s">
@@ -2603,7 +2603,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="155" t="s">
+      <c r="A9" s="73" t="s">
         <v>196</v>
       </c>
       <c r="B9" s="64" t="s">
@@ -2629,7 +2629,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="155" t="s">
+      <c r="A10" s="73" t="s">
         <v>195</v>
       </c>
       <c r="B10" s="64" t="s">
@@ -2655,7 +2655,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="155" t="s">
+      <c r="A11" s="73" t="s">
         <v>194</v>
       </c>
       <c r="B11" s="64" t="s">
@@ -2681,7 +2681,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="155" t="s">
+      <c r="A12" s="73" t="s">
         <v>193</v>
       </c>
       <c r="B12" s="64" t="s">
@@ -2707,7 +2707,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="155" t="s">
+      <c r="A13" s="73" t="s">
         <v>192</v>
       </c>
       <c r="B13" s="64" t="s">
@@ -2733,7 +2733,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="155" t="s">
+      <c r="A14" s="73" t="s">
         <v>191</v>
       </c>
       <c r="B14" s="64" t="s">
@@ -2759,7 +2759,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="155" t="s">
+      <c r="A15" s="73" t="s">
         <v>197</v>
       </c>
       <c r="B15" s="64" t="s">
@@ -2785,7 +2785,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="77" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="155" t="s">
+      <c r="A16" s="73" t="s">
         <v>190</v>
       </c>
       <c r="B16" s="64" t="s">
@@ -2811,7 +2811,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="155" t="s">
+      <c r="A17" s="73" t="s">
         <v>158</v>
       </c>
       <c r="B17" s="64" t="s">
@@ -2837,7 +2837,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="155" t="s">
+      <c r="A18" s="73" t="s">
         <v>159</v>
       </c>
       <c r="B18" s="64" t="s">
@@ -2863,7 +2863,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="155" t="s">
+      <c r="A19" s="73" t="s">
         <v>160</v>
       </c>
       <c r="B19" s="64" t="s">
@@ -2889,7 +2889,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="98" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="155" t="s">
+      <c r="A20" s="73" t="s">
         <v>161</v>
       </c>
       <c r="B20" s="64" t="s">
@@ -2915,7 +2915,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="88" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="155" t="s">
+      <c r="A21" s="73" t="s">
         <v>162</v>
       </c>
       <c r="B21" s="64" t="s">
@@ -2941,7 +2941,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="155" t="s">
+      <c r="A22" s="73" t="s">
         <v>163</v>
       </c>
       <c r="B22" s="64" t="s">
@@ -2967,7 +2967,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="63.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="155" t="s">
+      <c r="A23" s="73" t="s">
         <v>164</v>
       </c>
       <c r="B23" s="64" t="s">
@@ -2993,7 +2993,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="88.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="155" t="s">
+      <c r="A24" s="73" t="s">
         <v>189</v>
       </c>
       <c r="B24" s="64" t="s">
@@ -3019,7 +3019,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="88" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="155" t="s">
+      <c r="A25" s="73" t="s">
         <v>188</v>
       </c>
       <c r="B25" s="64" t="s">
@@ -3045,7 +3045,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="155" t="s">
+      <c r="A26" s="73" t="s">
         <v>187</v>
       </c>
       <c r="B26" s="64" t="s">
@@ -3071,7 +3071,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="78.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="155" t="s">
+      <c r="A27" s="73" t="s">
         <v>186</v>
       </c>
       <c r="B27" s="64" t="s">
@@ -3097,7 +3097,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="83.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="155" t="s">
+      <c r="A28" s="73" t="s">
         <v>185</v>
       </c>
       <c r="B28" s="64" t="s">
@@ -3123,7 +3123,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="90.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="155" t="s">
+      <c r="A29" s="73" t="s">
         <v>184</v>
       </c>
       <c r="B29" s="64" t="s">
@@ -3149,7 +3149,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="81.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="155" t="s">
+      <c r="A30" s="73" t="s">
         <v>183</v>
       </c>
       <c r="B30" s="64" t="s">
@@ -3175,7 +3175,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="155" t="s">
+      <c r="A31" s="73" t="s">
         <v>182</v>
       </c>
       <c r="B31" s="64" t="s">
@@ -3201,7 +3201,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="102" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="155" t="s">
+      <c r="A32" s="73" t="s">
         <v>247</v>
       </c>
       <c r="B32" s="64" t="s">
@@ -3227,7 +3227,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="93" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="155" t="s">
+      <c r="A33" s="73" t="s">
         <v>248</v>
       </c>
       <c r="B33" s="64" t="s">
@@ -3253,7 +3253,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="155" t="s">
+      <c r="A34" s="73" t="s">
         <v>249</v>
       </c>
       <c r="B34" s="64" t="s">
@@ -3279,7 +3279,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="82" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="155" t="s">
+      <c r="A35" s="73" t="s">
         <v>250</v>
       </c>
       <c r="B35" s="64" t="s">
@@ -3305,7 +3305,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="78.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="155" t="s">
+      <c r="A36" s="73" t="s">
         <v>251</v>
       </c>
       <c r="B36" s="64" t="s">
@@ -3331,7 +3331,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="88" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="155" t="s">
+      <c r="A37" s="73" t="s">
         <v>252</v>
       </c>
       <c r="B37" s="64" t="s">
@@ -3357,7 +3357,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="82" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="155" t="s">
+      <c r="A38" s="73" t="s">
         <v>253</v>
       </c>
       <c r="B38" s="64" t="s">
@@ -3383,7 +3383,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="106" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="155" t="s">
+      <c r="A39" s="73" t="s">
         <v>254</v>
       </c>
       <c r="B39" s="64" t="s">
@@ -3409,7 +3409,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="119.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="155" t="s">
+      <c r="A40" s="73" t="s">
         <v>255</v>
       </c>
       <c r="B40" s="64" t="s">
@@ -3435,7 +3435,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="84" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="155" t="s">
+      <c r="A41" s="73" t="s">
         <v>256</v>
       </c>
       <c r="B41" s="64" t="s">
@@ -3461,7 +3461,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="155" t="s">
+      <c r="A42" s="73" t="s">
         <v>257</v>
       </c>
       <c r="B42" s="64" t="s">
@@ -3487,7 +3487,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="106" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="155" t="s">
+      <c r="A43" s="73" t="s">
         <v>258</v>
       </c>
       <c r="B43" s="64" t="s">
@@ -3513,7 +3513,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="88.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="155" t="s">
+      <c r="A44" s="73" t="s">
         <v>259</v>
       </c>
       <c r="B44" s="64" t="s">
@@ -3539,7 +3539,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="114.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="155" t="s">
+      <c r="A45" s="73" t="s">
         <v>260</v>
       </c>
       <c r="B45" s="64" t="s">
@@ -3565,7 +3565,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="97.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="155" t="s">
+      <c r="A46" s="73" t="s">
         <v>261</v>
       </c>
       <c r="B46" s="64" t="s">
@@ -3591,7 +3591,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="155" t="s">
+      <c r="A47" s="73" t="s">
         <v>262</v>
       </c>
       <c r="B47" s="64" t="s">
@@ -3617,7 +3617,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="155" t="s">
+      <c r="A48" s="73" t="s">
         <v>206</v>
       </c>
       <c r="B48" s="64" t="s">
@@ -3643,7 +3643,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="155" t="s">
+      <c r="A49" s="73" t="s">
         <v>244</v>
       </c>
       <c r="B49" s="64" t="s">
@@ -3669,7 +3669,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="155" t="s">
+      <c r="A50" s="73" t="s">
         <v>207</v>
       </c>
       <c r="B50" s="64" t="s">
@@ -3695,7 +3695,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="77" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="155" t="s">
+      <c r="A51" s="73" t="s">
         <v>245</v>
       </c>
       <c r="B51" s="64" t="s">
@@ -3721,7 +3721,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="67" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="155" t="s">
+      <c r="A52" s="73" t="s">
         <v>208</v>
       </c>
       <c r="B52" s="64" t="s">
@@ -3747,7 +3747,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="155" t="s">
+      <c r="A53" s="73" t="s">
         <v>246</v>
       </c>
       <c r="B53" s="64" t="s">
@@ -3773,7 +3773,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="86" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="156" t="s">
+      <c r="A54" s="74" t="s">
         <v>263</v>
       </c>
       <c r="B54" s="64" t="s">
@@ -3799,7 +3799,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="155" t="s">
+      <c r="A55" s="73" t="s">
         <v>264</v>
       </c>
       <c r="B55" s="64" t="s">
@@ -3825,7 +3825,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="71" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="155" t="s">
+      <c r="A56" s="73" t="s">
         <v>265</v>
       </c>
       <c r="B56" s="64" t="s">
@@ -3851,7 +3851,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="76" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="155" t="s">
+      <c r="A57" s="73" t="s">
         <v>266</v>
       </c>
       <c r="B57" s="64" t="s">
@@ -3877,7 +3877,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="155" t="s">
+      <c r="A58" s="73" t="s">
         <v>267</v>
       </c>
       <c r="B58" s="64" t="s">
@@ -3903,7 +3903,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" ht="77" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="155" t="s">
+      <c r="A59" s="73" t="s">
         <v>268</v>
       </c>
       <c r="B59" s="64" t="s">
@@ -3929,7 +3929,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="71.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="155" t="s">
+      <c r="A60" s="73" t="s">
         <v>269</v>
       </c>
       <c r="B60" s="64" t="s">
@@ -3955,7 +3955,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="77" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="155" t="s">
+      <c r="A61" s="73" t="s">
         <v>270</v>
       </c>
       <c r="B61" s="64" t="s">
@@ -3981,7 +3981,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="78" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="155" t="s">
+      <c r="A62" s="73" t="s">
         <v>271</v>
       </c>
       <c r="B62" s="64" t="s">
@@ -4007,7 +4007,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="111" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="155" t="s">
+      <c r="A63" s="73" t="s">
         <v>272</v>
       </c>
       <c r="B63" s="64" t="s">
@@ -4033,7 +4033,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="111.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="155" t="s">
+      <c r="A64" s="73" t="s">
         <v>273</v>
       </c>
       <c r="B64" s="64" t="s">
@@ -4059,7 +4059,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="155" t="s">
+      <c r="A65" s="73" t="s">
         <v>211</v>
       </c>
       <c r="B65" s="64" t="s">
@@ -4085,7 +4085,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="116.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="157" t="s">
+      <c r="A66" s="75" t="s">
         <v>212</v>
       </c>
       <c r="B66" s="64" t="s">
@@ -4111,7 +4111,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="117" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="155" t="s">
+      <c r="A67" s="73" t="s">
         <v>213</v>
       </c>
       <c r="B67" s="64" t="s">
@@ -4137,7 +4137,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="105.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="158" t="s">
+      <c r="A68" s="76" t="s">
         <v>214</v>
       </c>
       <c r="B68" s="64" t="s">
@@ -4163,7 +4163,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="107.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="155" t="s">
+      <c r="A69" s="73" t="s">
         <v>215</v>
       </c>
       <c r="B69" s="64" t="s">
@@ -4189,7 +4189,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="103" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="155" t="s">
+      <c r="A70" s="73" t="s">
         <v>216</v>
       </c>
       <c r="B70" s="64" t="s">
@@ -4215,7 +4215,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="91.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="155" t="s">
+      <c r="A71" s="73" t="s">
         <v>217</v>
       </c>
       <c r="B71" s="64" t="s">
@@ -4241,7 +4241,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="155" t="s">
+      <c r="A72" s="73" t="s">
         <v>218</v>
       </c>
       <c r="B72" s="56" t="s">
@@ -4267,7 +4267,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="102.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="155" t="s">
+      <c r="A73" s="73" t="s">
         <v>219</v>
       </c>
       <c r="B73" s="56" t="s">
@@ -4293,7 +4293,7 @@
       </c>
     </row>
     <row r="74" spans="1:8" ht="106" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="155" t="s">
+      <c r="A74" s="73" t="s">
         <v>220</v>
       </c>
       <c r="B74" s="56" t="s">
@@ -4319,7 +4319,7 @@
       </c>
     </row>
     <row r="75" spans="1:8" ht="110.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="155" t="s">
+      <c r="A75" s="73" t="s">
         <v>221</v>
       </c>
       <c r="B75" s="56" t="s">
@@ -4345,7 +4345,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="155" t="s">
+      <c r="A76" s="73" t="s">
         <v>222</v>
       </c>
       <c r="B76" s="56" t="s">
@@ -4371,7 +4371,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="102" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="155" t="s">
+      <c r="A77" s="73" t="s">
         <v>223</v>
       </c>
       <c r="B77" s="56" t="s">
@@ -4397,7 +4397,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="100.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="155" t="s">
+      <c r="A78" s="73" t="s">
         <v>224</v>
       </c>
       <c r="B78" s="56" t="s">
@@ -4423,7 +4423,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="94.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="155" t="s">
+      <c r="A79" s="73" t="s">
         <v>225</v>
       </c>
       <c r="B79" s="56" t="s">
@@ -4449,7 +4449,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="155" t="s">
+      <c r="A80" s="73" t="s">
         <v>226</v>
       </c>
       <c r="B80" s="56" t="s">
@@ -4475,7 +4475,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="96.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="155" t="s">
+      <c r="A81" s="73" t="s">
         <v>227</v>
       </c>
       <c r="B81" s="56" t="s">
@@ -4501,7 +4501,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" ht="117.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="155" t="s">
+      <c r="A82" s="73" t="s">
         <v>228</v>
       </c>
       <c r="B82" s="56" t="s">
@@ -4527,7 +4527,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" ht="109" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="155" t="s">
+      <c r="A83" s="73" t="s">
         <v>229</v>
       </c>
       <c r="B83" s="56" t="s">
@@ -4587,25 +4587,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
       <c r="K1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="85" t="s">
+      <c r="L1" s="89" t="s">
         <v>135</v>
       </c>
-      <c r="M1" s="85"/>
+      <c r="M1" s="89"/>
     </row>
     <row r="2" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="35"/>
@@ -4622,10 +4622,10 @@
       <c r="L2" s="36"/>
     </row>
     <row r="3" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="85" t="s">
+      <c r="A3" s="89" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="85"/>
+      <c r="B3" s="89"/>
       <c r="C3" s="36"/>
       <c r="D3" s="36"/>
       <c r="E3" s="53"/>
@@ -4637,10 +4637,10 @@
       <c r="K3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="85" t="s">
+      <c r="L3" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="85"/>
+      <c r="M3" s="89"/>
     </row>
     <row r="4" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
@@ -4657,62 +4657,62 @@
       <c r="L4" s="7"/>
     </row>
     <row r="5" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="78" t="s">
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="78"/>
-      <c r="L5" s="78"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
     </row>
     <row r="6" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="78" t="s">
+      <c r="B6" s="87"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="87"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="78"/>
-      <c r="L6" s="78"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
     </row>
     <row r="7" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="78" t="s">
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="K7" s="78"/>
-      <c r="L7" s="78"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
     </row>
     <row r="8" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="79"/>
-      <c r="B8" s="79"/>
+      <c r="A8" s="83"/>
+      <c r="B8" s="83"/>
       <c r="C8" s="39"/>
       <c r="D8" s="39"/>
       <c r="E8" s="54"/>
@@ -4720,9 +4720,9 @@
       <c r="G8" s="54"/>
       <c r="H8" s="54"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="80"/>
+      <c r="J8" s="84"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="84"/>
     </row>
     <row r="9" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="40"/>
@@ -4739,26 +4739,26 @@
       <c r="L9" s="40"/>
     </row>
     <row r="10" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="81"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="85"/>
+      <c r="K10" s="85"/>
       <c r="L10" s="40"/>
     </row>
     <row r="11" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="143" t="s">
+      <c r="A11" s="147" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="144"/>
+      <c r="B11" s="148"/>
       <c r="C11" s="66" t="s">
         <v>75</v>
       </c>
@@ -4771,21 +4771,21 @@
       <c r="F11" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="142" t="s">
+      <c r="G11" s="146" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="142"/>
-      <c r="I11" s="142" t="s">
+      <c r="H11" s="146"/>
+      <c r="I11" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="142"/>
+      <c r="J11" s="146"/>
       <c r="K11" s="67" t="s">
         <v>83</v>
       </c>
       <c r="L11" s="40"/>
     </row>
     <row r="12" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="145" t="s">
+      <c r="A12" s="149" t="s">
         <v>92</v>
       </c>
       <c r="B12" s="41" t="s">
@@ -4797,17 +4797,17 @@
       </c>
       <c r="E12" s="41"/>
       <c r="F12" s="42"/>
-      <c r="G12" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="H12" s="140"/>
-      <c r="I12" s="141"/>
-      <c r="J12" s="141"/>
+      <c r="G12" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="144"/>
+      <c r="I12" s="145"/>
+      <c r="J12" s="145"/>
       <c r="K12" s="68"/>
       <c r="L12" s="40"/>
     </row>
     <row r="13" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="147"/>
+      <c r="A13" s="151"/>
       <c r="B13" s="41" t="s">
         <v>81</v>
       </c>
@@ -4817,17 +4817,17 @@
       <c r="D13" s="41"/>
       <c r="E13" s="41"/>
       <c r="F13" s="42"/>
-      <c r="G13" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="H13" s="140"/>
-      <c r="I13" s="141"/>
-      <c r="J13" s="141"/>
+      <c r="G13" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13" s="144"/>
+      <c r="I13" s="145"/>
+      <c r="J13" s="145"/>
       <c r="K13" s="68"/>
       <c r="L13" s="40"/>
     </row>
     <row r="14" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="148" t="s">
+      <c r="A14" s="152" t="s">
         <v>93</v>
       </c>
       <c r="B14" s="41" t="s">
@@ -4839,17 +4839,17 @@
       </c>
       <c r="E14" s="41"/>
       <c r="F14" s="42"/>
-      <c r="G14" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="H14" s="140"/>
-      <c r="I14" s="141"/>
-      <c r="J14" s="141"/>
+      <c r="G14" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="144"/>
+      <c r="I14" s="145"/>
+      <c r="J14" s="145"/>
       <c r="K14" s="68"/>
       <c r="L14" s="40"/>
     </row>
     <row r="15" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="150"/>
+      <c r="A15" s="154"/>
       <c r="B15" s="41" t="s">
         <v>81</v>
       </c>
@@ -4859,17 +4859,17 @@
       <c r="D15" s="43"/>
       <c r="E15" s="43"/>
       <c r="F15" s="42"/>
-      <c r="G15" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="H15" s="140"/>
-      <c r="I15" s="141"/>
-      <c r="J15" s="141"/>
+      <c r="G15" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="144"/>
+      <c r="I15" s="145"/>
+      <c r="J15" s="145"/>
       <c r="K15" s="68"/>
       <c r="L15" s="40"/>
     </row>
     <row r="16" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="149" t="s">
         <v>94</v>
       </c>
       <c r="B16" s="41" t="s">
@@ -4881,17 +4881,17 @@
       <c r="F16" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="G16" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="H16" s="140"/>
-      <c r="I16" s="141"/>
-      <c r="J16" s="141"/>
+      <c r="G16" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" s="144"/>
+      <c r="I16" s="145"/>
+      <c r="J16" s="145"/>
       <c r="K16" s="68"/>
       <c r="L16" s="40"/>
     </row>
     <row r="17" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="147"/>
+      <c r="A17" s="151"/>
       <c r="B17" s="41" t="s">
         <v>81</v>
       </c>
@@ -4901,258 +4901,258 @@
         <v>95</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="H17" s="140"/>
-      <c r="I17" s="141"/>
-      <c r="J17" s="141"/>
+      <c r="G17" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="144"/>
+      <c r="I17" s="145"/>
+      <c r="J17" s="145"/>
       <c r="K17" s="68"/>
       <c r="L17" s="40"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18" s="92" t="s">
+      <c r="A18" s="96" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="93"/>
-      <c r="C18" s="92" t="s">
+      <c r="B18" s="97"/>
+      <c r="C18" s="96" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="93"/>
-      <c r="E18" s="81" t="s">
+      <c r="D18" s="97"/>
+      <c r="E18" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81" t="s">
+      <c r="F18" s="85"/>
+      <c r="G18" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="81"/>
-      <c r="I18" s="92" t="s">
+      <c r="H18" s="85"/>
+      <c r="I18" s="96" t="s">
         <v>83</v>
       </c>
-      <c r="J18" s="93"/>
+      <c r="J18" s="97"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19" s="145" t="s">
+      <c r="A19" s="149" t="s">
         <v>88</v>
       </c>
       <c r="B19" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="151" t="s">
+      <c r="C19" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="152"/>
-      <c r="E19" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" s="140"/>
-      <c r="G19" s="81"/>
-      <c r="H19" s="81"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="D19" s="156"/>
+      <c r="E19" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" s="144"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="85"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="94"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20" s="146"/>
+      <c r="A20" s="150"/>
       <c r="B20" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="151" t="s">
+      <c r="C20" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="152"/>
-      <c r="E20" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="F20" s="140"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="90"/>
+      <c r="D20" s="156"/>
+      <c r="E20" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="144"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="94"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21" s="146"/>
+      <c r="A21" s="150"/>
       <c r="B21" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="151" t="s">
+      <c r="C21" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="D21" s="152"/>
-      <c r="E21" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" s="140"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="D21" s="156"/>
+      <c r="E21" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" s="144"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="93"/>
+      <c r="J21" s="94"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22" s="147"/>
+      <c r="A22" s="151"/>
       <c r="B22" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="151" t="s">
+      <c r="C22" s="155" t="s">
         <v>126</v>
       </c>
-      <c r="D22" s="152"/>
-      <c r="E22" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22" s="140"/>
-      <c r="G22" s="81"/>
-      <c r="H22" s="81"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="D22" s="156"/>
+      <c r="E22" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="144"/>
+      <c r="G22" s="85"/>
+      <c r="H22" s="85"/>
+      <c r="I22" s="93"/>
+      <c r="J22" s="94"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23" s="148" t="s">
+      <c r="A23" s="152" t="s">
         <v>89</v>
       </c>
       <c r="B23" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="151" t="s">
+      <c r="C23" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="D23" s="152"/>
-      <c r="E23" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="140"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="144"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="93"/>
+      <c r="J23" s="94"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24" s="149"/>
+      <c r="A24" s="153"/>
       <c r="B24" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="151" t="s">
+      <c r="C24" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="D24" s="152"/>
-      <c r="E24" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24" s="140"/>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="90"/>
+      <c r="D24" s="156"/>
+      <c r="E24" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" s="144"/>
+      <c r="G24" s="85"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="94"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25" s="149"/>
+      <c r="A25" s="153"/>
       <c r="B25" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="151" t="s">
+      <c r="C25" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="D25" s="152"/>
-      <c r="E25" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="140"/>
-      <c r="G25" s="81"/>
-      <c r="H25" s="81"/>
-      <c r="I25" s="89"/>
-      <c r="J25" s="90"/>
+      <c r="D25" s="156"/>
+      <c r="E25" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="144"/>
+      <c r="G25" s="85"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="93"/>
+      <c r="J25" s="94"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="150"/>
+      <c r="A26" s="154"/>
       <c r="B26" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="151" t="s">
+      <c r="C26" s="155" t="s">
         <v>126</v>
       </c>
-      <c r="D26" s="152"/>
-      <c r="E26" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" s="140"/>
-      <c r="G26" s="81"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="153"/>
-      <c r="J26" s="154"/>
+      <c r="D26" s="156"/>
+      <c r="E26" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" s="144"/>
+      <c r="G26" s="85"/>
+      <c r="H26" s="85"/>
+      <c r="I26" s="157"/>
+      <c r="J26" s="158"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27" s="145" t="s">
+      <c r="A27" s="149" t="s">
         <v>90</v>
       </c>
       <c r="B27" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="151" t="s">
+      <c r="C27" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="D27" s="152"/>
-      <c r="E27" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="F27" s="140"/>
-      <c r="G27" s="81"/>
-      <c r="H27" s="81"/>
-      <c r="I27" s="89"/>
-      <c r="J27" s="90"/>
+      <c r="D27" s="156"/>
+      <c r="E27" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="144"/>
+      <c r="G27" s="85"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="94"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28" s="146"/>
+      <c r="A28" s="150"/>
       <c r="B28" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="151" t="s">
+      <c r="C28" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="152"/>
-      <c r="E28" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="F28" s="140"/>
-      <c r="G28" s="81"/>
-      <c r="H28" s="81"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="90"/>
+      <c r="D28" s="156"/>
+      <c r="E28" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28" s="144"/>
+      <c r="G28" s="85"/>
+      <c r="H28" s="85"/>
+      <c r="I28" s="93"/>
+      <c r="J28" s="94"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29" s="146"/>
+      <c r="A29" s="150"/>
       <c r="B29" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="151" t="s">
+      <c r="C29" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="D29" s="152"/>
-      <c r="E29" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="F29" s="140"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="89"/>
-      <c r="J29" s="90"/>
+      <c r="D29" s="156"/>
+      <c r="E29" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="144"/>
+      <c r="G29" s="85"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="93"/>
+      <c r="J29" s="94"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30" s="147"/>
+      <c r="A30" s="151"/>
       <c r="B30" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="151" t="s">
+      <c r="C30" s="155" t="s">
         <v>126</v>
       </c>
-      <c r="D30" s="152"/>
-      <c r="E30" s="140" t="s">
-        <v>95</v>
-      </c>
-      <c r="F30" s="140"/>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="90"/>
+      <c r="D30" s="156"/>
+      <c r="E30" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30" s="144"/>
+      <c r="G30" s="85"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="87">
@@ -5259,18 +5259,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="85" t="s">
+      <c r="E1" s="89" t="s">
         <v>128</v>
       </c>
-      <c r="F1" s="85"/>
+      <c r="F1" s="89"/>
     </row>
     <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
@@ -5280,18 +5280,18 @@
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="85" t="s">
+      <c r="A3" s="89" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="85"/>
+      <c r="B3" s="89"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="85" t="s">
+      <c r="E3" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="85"/>
+      <c r="F3" s="89"/>
     </row>
     <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
@@ -5301,44 +5301,44 @@
       <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="78" t="s">
+      <c r="B5" s="87"/>
+      <c r="C5" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
     </row>
     <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="78" t="s">
+      <c r="B6" s="87"/>
+      <c r="C6" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
     </row>
     <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="78" t="s">
+      <c r="B7" s="87"/>
+      <c r="C7" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
     </row>
     <row r="8" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="79"/>
-      <c r="B8" s="79"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
+      <c r="A8" s="83"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
     </row>
     <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="8"/>
@@ -5348,19 +5348,19 @@
       <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="81"/>
-      <c r="C10" s="81"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
       <c r="D10" s="14"/>
       <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="82" t="s">
+      <c r="A11" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="82"/>
+      <c r="B11" s="86"/>
       <c r="C11" s="45" t="s">
         <v>95</v>
       </c>
@@ -5368,10 +5368,10 @@
       <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="81" t="s">
         <v>198</v>
       </c>
-      <c r="B12" s="77"/>
+      <c r="B12" s="81"/>
       <c r="C12" s="45" t="s">
         <v>95</v>
       </c>
@@ -5379,10 +5379,10 @@
       <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="77" t="s">
+      <c r="A13" s="81" t="s">
         <v>199</v>
       </c>
-      <c r="B13" s="77"/>
+      <c r="B13" s="81"/>
       <c r="C13" s="45" t="s">
         <v>95</v>
       </c>
@@ -5390,10 +5390,10 @@
       <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="92" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="87"/>
+      <c r="B14" s="91"/>
       <c r="C14" s="45" t="s">
         <v>95</v>
       </c>
@@ -5401,10 +5401,10 @@
       <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="B15" s="77"/>
+      <c r="B15" s="81"/>
       <c r="C15" s="45" t="s">
         <v>95</v>
       </c>
@@ -5412,10 +5412,10 @@
       <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="81" t="s">
         <v>202</v>
       </c>
-      <c r="B16" s="77"/>
+      <c r="B16" s="81"/>
       <c r="C16" s="45" t="s">
         <v>95</v>
       </c>
@@ -5423,10 +5423,10 @@
       <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="90" t="s">
         <v>203</v>
       </c>
-      <c r="B17" s="87"/>
+      <c r="B17" s="91"/>
       <c r="C17" s="45" t="s">
         <v>95</v>
       </c>
@@ -5434,10 +5434,10 @@
       <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="86" t="s">
+      <c r="A18" s="90" t="s">
         <v>204</v>
       </c>
-      <c r="B18" s="87"/>
+      <c r="B18" s="91"/>
       <c r="C18" s="45" t="s">
         <v>95</v>
       </c>
@@ -5445,10 +5445,10 @@
       <c r="E18" s="8"/>
     </row>
     <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="86" t="s">
+      <c r="A19" s="90" t="s">
         <v>205</v>
       </c>
-      <c r="B19" s="87"/>
+      <c r="B19" s="91"/>
       <c r="C19" s="45" t="s">
         <v>95</v>
       </c>
@@ -5456,10 +5456,10 @@
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="90"/>
+      <c r="B20" s="94"/>
       <c r="C20" s="45" t="s">
         <v>95</v>
       </c>
@@ -5467,10 +5467,10 @@
       <c r="E20" s="12"/>
     </row>
     <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="86" t="s">
+      <c r="A21" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="87"/>
+      <c r="B21" s="91"/>
       <c r="C21" s="45" t="s">
         <v>95</v>
       </c>
@@ -5478,10 +5478,10 @@
       <c r="E21" s="12"/>
     </row>
     <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="86" t="s">
+      <c r="A22" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="87"/>
+      <c r="B22" s="91"/>
       <c r="C22" s="45" t="s">
         <v>95</v>
       </c>
@@ -5489,10 +5489,10 @@
       <c r="E22" s="12"/>
     </row>
     <row r="23" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="86" t="s">
+      <c r="A23" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="87"/>
+      <c r="B23" s="91"/>
       <c r="C23" s="45" t="s">
         <v>95</v>
       </c>
@@ -5500,10 +5500,10 @@
       <c r="E23" s="12"/>
     </row>
     <row r="24" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="86" t="s">
+      <c r="A24" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="87"/>
+      <c r="B24" s="91"/>
       <c r="C24" s="45" t="s">
         <v>95</v>
       </c>
@@ -5511,10 +5511,10 @@
       <c r="E24" s="12"/>
     </row>
     <row r="25" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="86" t="s">
+      <c r="A25" s="90" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="87"/>
+      <c r="B25" s="91"/>
       <c r="C25" s="45" t="s">
         <v>95</v>
       </c>
@@ -5522,10 +5522,10 @@
       <c r="E25" s="12"/>
     </row>
     <row r="26" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="86" t="s">
+      <c r="A26" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="87"/>
+      <c r="B26" s="91"/>
       <c r="C26" s="45" t="s">
         <v>95</v>
       </c>
@@ -5533,15 +5533,15 @@
       <c r="E26" s="12"/>
     </row>
     <row r="27" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="86"/>
-      <c r="B27" s="87"/>
+      <c r="A27" s="90"/>
+      <c r="B27" s="91"/>
       <c r="C27" s="15"/>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
     </row>
     <row r="28" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="77"/>
-      <c r="B28" s="77"/>
+      <c r="A28" s="81"/>
+      <c r="B28" s="81"/>
       <c r="C28" s="15"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
@@ -5597,19 +5597,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
       <c r="E1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="85" t="s">
+      <c r="F1" s="89" t="s">
         <v>129</v>
       </c>
-      <c r="G1" s="85"/>
+      <c r="G1" s="89"/>
     </row>
     <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
@@ -5620,19 +5620,19 @@
       <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="85" t="s">
+      <c r="A3" s="89" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="85"/>
+      <c r="B3" s="89"/>
       <c r="C3" s="4"/>
       <c r="D3" s="10"/>
       <c r="E3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="85" t="s">
+      <c r="F3" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="85"/>
+      <c r="G3" s="89"/>
     </row>
     <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
@@ -5643,48 +5643,48 @@
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="78" t="s">
+      <c r="B5" s="87"/>
+      <c r="C5" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
     </row>
     <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="78" t="s">
+      <c r="B6" s="87"/>
+      <c r="C6" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
     </row>
     <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="78" t="s">
+      <c r="B7" s="87"/>
+      <c r="C7" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
     </row>
     <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="79"/>
-      <c r="B8" s="79"/>
+      <c r="A8" s="83"/>
+      <c r="B8" s="83"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
     </row>
     <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
@@ -5695,10 +5695,10 @@
       <c r="F9" s="12"/>
     </row>
     <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="92" t="s">
+      <c r="A10" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="93"/>
+      <c r="B10" s="97"/>
       <c r="C10" s="13" t="s">
         <v>35</v>
       </c>
@@ -5711,10 +5711,10 @@
       <c r="F10" s="69"/>
     </row>
     <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="82" t="s">
+      <c r="A11" s="86" t="s">
         <v>174</v>
       </c>
-      <c r="B11" s="82"/>
+      <c r="B11" s="86"/>
       <c r="C11" s="45" t="s">
         <v>95</v>
       </c>
@@ -5727,10 +5727,10 @@
       <c r="F11" s="70"/>
     </row>
     <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="82" t="s">
+      <c r="A12" s="86" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="82"/>
+      <c r="B12" s="86"/>
       <c r="C12" s="45" t="s">
         <v>95</v>
       </c>
@@ -5743,10 +5743,10 @@
       <c r="F12" s="70"/>
     </row>
     <row r="13" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="91" t="s">
+      <c r="A13" s="95" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="90"/>
+      <c r="B13" s="94"/>
       <c r="C13" s="45" t="s">
         <v>95</v>
       </c>
@@ -5759,10 +5759,10 @@
       <c r="F13" s="70"/>
     </row>
     <row r="14" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="82" t="s">
+      <c r="A14" s="86" t="s">
         <v>177</v>
       </c>
-      <c r="B14" s="82"/>
+      <c r="B14" s="86"/>
       <c r="C14" s="45" t="s">
         <v>95</v>
       </c>
@@ -5775,10 +5775,10 @@
       <c r="F14" s="70"/>
     </row>
     <row r="15" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="82" t="s">
+      <c r="A15" s="86" t="s">
         <v>178</v>
       </c>
-      <c r="B15" s="82"/>
+      <c r="B15" s="86"/>
       <c r="C15" s="45" t="s">
         <v>95</v>
       </c>
@@ -5791,10 +5791,10 @@
       <c r="F15" s="70"/>
     </row>
     <row r="16" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="89" t="s">
+      <c r="A16" s="93" t="s">
         <v>179</v>
       </c>
-      <c r="B16" s="90"/>
+      <c r="B16" s="94"/>
       <c r="C16" s="45" t="s">
         <v>95</v>
       </c>
@@ -5807,10 +5807,10 @@
       <c r="F16" s="70"/>
     </row>
     <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="93" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="90"/>
+      <c r="B17" s="94"/>
       <c r="C17" s="45" t="s">
         <v>95</v>
       </c>
@@ -5823,10 +5823,10 @@
       <c r="F17" s="70"/>
     </row>
     <row r="18" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="89" t="s">
+      <c r="A18" s="93" t="s">
         <v>181</v>
       </c>
-      <c r="B18" s="90"/>
+      <c r="B18" s="94"/>
       <c r="C18" s="45" t="s">
         <v>95</v>
       </c>
@@ -5888,94 +5888,94 @@
       <c r="C1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="97" t="s">
+      <c r="D1" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="99"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="103"/>
     </row>
     <row r="2" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="100" t="s">
+      <c r="B2" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="101"/>
+      <c r="C2" s="105"/>
       <c r="D2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="100" t="s">
+      <c r="E2" s="104" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="103"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="107"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="104" t="s">
+      <c r="A3" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="99"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="103"/>
     </row>
     <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="19">
         <v>1</v>
       </c>
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="98" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="96"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="100"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>2</v>
       </c>
-      <c r="B5" s="100" t="s">
+      <c r="B5" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="103"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="107"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="106" t="s">
+      <c r="A6" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="99"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="103"/>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="107" t="s">
+      <c r="A7" s="111" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="108"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="110" t="s">
+      <c r="B7" s="112"/>
+      <c r="C7" s="113"/>
+      <c r="D7" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="109"/>
+      <c r="E7" s="113"/>
       <c r="F7" s="50" t="s">
         <v>20</v>
       </c>
@@ -5990,14 +5990,14 @@
       <c r="A8" s="19">
         <v>1</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="98" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="111"/>
-      <c r="D8" s="94" t="s">
+      <c r="C8" s="115"/>
+      <c r="D8" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E8" s="112"/>
+      <c r="E8" s="116"/>
       <c r="F8" s="46"/>
       <c r="G8" s="46" t="s">
         <v>96</v>
@@ -6010,14 +6010,14 @@
       <c r="A9" s="19">
         <v>2</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="94" t="s">
+      <c r="C9" s="115"/>
+      <c r="D9" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E9" s="112"/>
+      <c r="E9" s="116"/>
       <c r="F9" s="21"/>
       <c r="G9" s="46" t="s">
         <v>96</v>
@@ -6030,14 +6030,14 @@
       <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="94" t="s">
+      <c r="B10" s="98" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="94" t="s">
+      <c r="C10" s="115"/>
+      <c r="D10" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E10" s="112"/>
+      <c r="E10" s="116"/>
       <c r="F10" s="46" t="s">
         <v>95</v>
       </c>
@@ -6048,14 +6048,14 @@
       <c r="A11" s="19">
         <v>4</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="111"/>
-      <c r="D11" s="94" t="s">
+      <c r="C11" s="115"/>
+      <c r="D11" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E11" s="112"/>
+      <c r="E11" s="116"/>
       <c r="F11" s="46" t="s">
         <v>95</v>
       </c>
@@ -6066,14 +6066,14 @@
       <c r="A12" s="19">
         <v>5</v>
       </c>
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="111"/>
-      <c r="D12" s="100" t="s">
+      <c r="C12" s="115"/>
+      <c r="D12" s="104" t="s">
         <v>243</v>
       </c>
-      <c r="E12" s="120"/>
+      <c r="E12" s="124"/>
       <c r="F12" s="46" t="s">
         <v>95</v>
       </c>
@@ -6084,14 +6084,14 @@
       <c r="A13" s="19">
         <v>6</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="98" t="s">
         <v>240</v>
       </c>
-      <c r="C13" s="111"/>
-      <c r="D13" s="100" t="s">
+      <c r="C13" s="115"/>
+      <c r="D13" s="104" t="s">
         <v>243</v>
       </c>
-      <c r="E13" s="120"/>
+      <c r="E13" s="124"/>
       <c r="F13" s="46" t="s">
         <v>95</v>
       </c>
@@ -6102,14 +6102,14 @@
       <c r="A14" s="23">
         <v>7</v>
       </c>
-      <c r="B14" s="100" t="s">
+      <c r="B14" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="120"/>
-      <c r="D14" s="100" t="s">
+      <c r="C14" s="124"/>
+      <c r="D14" s="104" t="s">
         <v>243</v>
       </c>
-      <c r="E14" s="120"/>
+      <c r="E14" s="124"/>
       <c r="F14" s="46" t="s">
         <v>95</v>
       </c>
@@ -6117,22 +6117,22 @@
       <c r="H14" s="25"/>
     </row>
     <row r="15" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="113" t="s">
+      <c r="A15" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="114"/>
-      <c r="C15" s="115" t="s">
+      <c r="B15" s="118"/>
+      <c r="C15" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="116"/>
+      <c r="D15" s="120"/>
       <c r="E15" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="117">
+      <c r="F15" s="121">
         <v>46227</v>
       </c>
-      <c r="G15" s="118"/>
-      <c r="H15" s="119"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -6189,13 +6189,13 @@
       <c r="B1" s="47" t="s">
         <v>152</v>
       </c>
-      <c r="C1" s="126"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="47" t="s">
@@ -6211,11 +6211,11 @@
       <c r="E2" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="122" t="s">
+      <c r="F2" s="126" t="s">
         <v>125</v>
       </c>
-      <c r="G2" s="128"/>
-      <c r="H2" s="129"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="133"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="47" t="s">
@@ -6233,297 +6233,297 @@
       <c r="E3" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="F3" s="122" t="s">
+      <c r="F3" s="126" t="s">
         <v>97</v>
       </c>
-      <c r="G3" s="128"/>
-      <c r="H3" s="129"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="133"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="122" t="s">
+      <c r="B4" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="129"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="132"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="133"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="121" t="s">
+      <c r="B5" s="125" t="s">
         <v>239</v>
       </c>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="B6" s="121" t="s">
+      <c r="B6" s="125" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="121"/>
+      <c r="C6" s="125"/>
+      <c r="D6" s="125"/>
+      <c r="E6" s="125"/>
+      <c r="F6" s="125"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="125"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="122" t="s">
+      <c r="A7" s="126" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="123"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="123"/>
-      <c r="H7" s="124"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="128"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="122" t="s">
+      <c r="A8" s="126" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="123"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="123"/>
-      <c r="H8" s="124"/>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="128"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="125" t="s">
+      <c r="A9" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="125"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125"/>
-      <c r="H9" s="125"/>
+      <c r="B9" s="129"/>
+      <c r="C9" s="129"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="47">
         <v>1</v>
       </c>
-      <c r="B10" s="121" t="s">
+      <c r="B10" s="125" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="47">
         <v>2</v>
       </c>
-      <c r="B11" s="121" t="s">
+      <c r="B11" s="125" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="125" t="s">
+      <c r="A12" s="129" t="s">
         <v>109</v>
       </c>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
+      <c r="B12" s="129"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="47">
         <v>1</v>
       </c>
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="125" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="121"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="121"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="47">
         <v>2</v>
       </c>
-      <c r="B14" s="121" t="s">
+      <c r="B14" s="125" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="121"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="121"/>
-      <c r="G14" s="121"/>
-      <c r="H14" s="121"/>
+      <c r="C14" s="125"/>
+      <c r="D14" s="125"/>
+      <c r="E14" s="125"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="47">
         <v>3</v>
       </c>
-      <c r="B15" s="121"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="121"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="47">
         <v>4</v>
       </c>
-      <c r="B16" s="121"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="121"/>
-      <c r="F16" s="121"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="121"/>
+      <c r="B16" s="125"/>
+      <c r="C16" s="125"/>
+      <c r="D16" s="125"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="125"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="47">
         <v>5</v>
       </c>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
+      <c r="B17" s="125"/>
+      <c r="C17" s="125"/>
+      <c r="D17" s="125"/>
+      <c r="E17" s="125"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="125" t="s">
+      <c r="A18" s="129" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="125"/>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="125"/>
-      <c r="H18" s="125"/>
+      <c r="B18" s="129"/>
+      <c r="C18" s="129"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="129"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="121" t="s">
+      <c r="A19" s="125" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="121"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="121"/>
-      <c r="H19" s="121"/>
+      <c r="B19" s="125"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="121" t="s">
+      <c r="A20" s="125" t="s">
         <v>122</v>
       </c>
-      <c r="B20" s="121"/>
-      <c r="C20" s="121"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="121"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="121"/>
+      <c r="B20" s="125"/>
+      <c r="C20" s="125"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="125"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="121"/>
-      <c r="B21" s="121"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="121"/>
-      <c r="G21" s="121"/>
-      <c r="H21" s="121"/>
+      <c r="A21" s="125"/>
+      <c r="B21" s="125"/>
+      <c r="C21" s="125"/>
+      <c r="D21" s="125"/>
+      <c r="E21" s="125"/>
+      <c r="F21" s="125"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="125"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="125" t="s">
+      <c r="A22" s="129" t="s">
         <v>123</v>
       </c>
-      <c r="B22" s="125"/>
-      <c r="C22" s="125"/>
-      <c r="D22" s="125"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="125"/>
-      <c r="G22" s="125"/>
-      <c r="H22" s="125"/>
+      <c r="B22" s="129"/>
+      <c r="C22" s="129"/>
+      <c r="D22" s="129"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="129"/>
+      <c r="H22" s="129"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="121" t="s">
+      <c r="A23" s="125" t="s">
         <v>124</v>
       </c>
-      <c r="B23" s="121"/>
-      <c r="C23" s="121"/>
-      <c r="D23" s="121"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="121"/>
-      <c r="G23" s="121"/>
-      <c r="H23" s="121"/>
+      <c r="B23" s="125"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="125"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="121"/>
-      <c r="B24" s="121"/>
-      <c r="C24" s="121"/>
-      <c r="D24" s="121"/>
-      <c r="E24" s="121"/>
-      <c r="F24" s="121"/>
-      <c r="G24" s="121"/>
-      <c r="H24" s="121"/>
+      <c r="A24" s="125"/>
+      <c r="B24" s="125"/>
+      <c r="C24" s="125"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
     </row>
     <row r="25" spans="1:8" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="121"/>
-      <c r="C25" s="121"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="121"/>
-      <c r="G25" s="121"/>
-      <c r="H25" s="121"/>
+      <c r="B25" s="125"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="125"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="125"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="121"/>
-      <c r="C26" s="121"/>
-      <c r="D26" s="121"/>
-      <c r="E26" s="121"/>
-      <c r="F26" s="121"/>
-      <c r="G26" s="121"/>
-      <c r="H26" s="121"/>
+      <c r="B26" s="125"/>
+      <c r="C26" s="125"/>
+      <c r="D26" s="125"/>
+      <c r="E26" s="125"/>
+      <c r="F26" s="125"/>
+      <c r="G26" s="125"/>
+      <c r="H26" s="125"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="49"/>
@@ -6601,94 +6601,94 @@
       <c r="C1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="97" t="s">
+      <c r="D1" s="101" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="99"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="103"/>
     </row>
     <row r="2" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="100" t="s">
+      <c r="B2" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="101"/>
+      <c r="C2" s="105"/>
       <c r="D2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="100" t="s">
+      <c r="E2" s="104" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="103"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="107"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="104" t="s">
+      <c r="A3" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="99"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="103"/>
     </row>
     <row r="4" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19">
         <v>1</v>
       </c>
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="98" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="96"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="100"/>
     </row>
     <row r="5" spans="1:8" ht="16.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>2</v>
       </c>
-      <c r="B5" s="100" t="s">
+      <c r="B5" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="103"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="107"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="106" t="s">
+      <c r="A6" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="99"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="103"/>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="95"/>
-      <c r="C7" s="112"/>
-      <c r="D7" s="131" t="s">
+      <c r="B7" s="99"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="135" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="112"/>
+      <c r="E7" s="116"/>
       <c r="F7" s="21" t="s">
         <v>20</v>
       </c>
@@ -6703,14 +6703,14 @@
       <c r="A8" s="19">
         <v>1</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="112"/>
-      <c r="D8" s="94" t="s">
+      <c r="C8" s="116"/>
+      <c r="D8" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E8" s="112"/>
+      <c r="E8" s="116"/>
       <c r="F8" s="46" t="s">
         <v>95</v>
       </c>
@@ -6721,14 +6721,14 @@
       <c r="A9" s="19">
         <v>2</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="98" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="112"/>
-      <c r="D9" s="94" t="s">
+      <c r="C9" s="116"/>
+      <c r="D9" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E9" s="112"/>
+      <c r="E9" s="116"/>
       <c r="F9" s="46" t="s">
         <v>95</v>
       </c>
@@ -6739,14 +6739,14 @@
       <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="94" t="s">
+      <c r="B10" s="98" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="112"/>
-      <c r="D10" s="94" t="s">
+      <c r="C10" s="116"/>
+      <c r="D10" s="98" t="s">
         <v>243</v>
       </c>
-      <c r="E10" s="112"/>
+      <c r="E10" s="116"/>
       <c r="F10" s="46" t="s">
         <v>95</v>
       </c>
@@ -6757,14 +6757,14 @@
       <c r="A11" s="19">
         <v>4</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="98" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="112"/>
-      <c r="D11" s="94" t="s">
+      <c r="C11" s="116"/>
+      <c r="D11" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E11" s="112"/>
+      <c r="E11" s="116"/>
       <c r="F11" s="46" t="s">
         <v>95</v>
       </c>
@@ -6775,14 +6775,14 @@
       <c r="A12" s="19">
         <v>5</v>
       </c>
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="112"/>
-      <c r="D12" s="94" t="s">
+      <c r="C12" s="116"/>
+      <c r="D12" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E12" s="112"/>
+      <c r="E12" s="116"/>
       <c r="F12" s="46" t="s">
         <v>95</v>
       </c>
@@ -6793,14 +6793,14 @@
       <c r="A13" s="19">
         <v>6</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="112"/>
-      <c r="D13" s="94" t="s">
+      <c r="C13" s="116"/>
+      <c r="D13" s="98" t="s">
         <v>243</v>
       </c>
-      <c r="E13" s="112"/>
+      <c r="E13" s="116"/>
       <c r="F13" s="46" t="s">
         <v>95</v>
       </c>
@@ -6811,14 +6811,14 @@
       <c r="A14" s="23">
         <v>7</v>
       </c>
-      <c r="B14" s="94" t="s">
+      <c r="B14" s="98" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="111"/>
-      <c r="D14" s="94" t="s">
+      <c r="C14" s="115"/>
+      <c r="D14" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E14" s="112"/>
+      <c r="E14" s="116"/>
       <c r="F14" s="46" t="s">
         <v>95</v>
       </c>
@@ -6829,14 +6829,14 @@
       <c r="A15" s="23">
         <v>8</v>
       </c>
-      <c r="B15" s="94" t="s">
+      <c r="B15" s="98" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="111"/>
-      <c r="D15" s="94" t="s">
+      <c r="C15" s="115"/>
+      <c r="D15" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E15" s="112"/>
+      <c r="E15" s="116"/>
       <c r="F15" s="46" t="s">
         <v>95</v>
       </c>
@@ -6847,14 +6847,14 @@
       <c r="A16" s="23">
         <v>9</v>
       </c>
-      <c r="B16" s="132" t="s">
+      <c r="B16" s="136" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="133"/>
-      <c r="D16" s="100" t="s">
+      <c r="C16" s="137"/>
+      <c r="D16" s="104" t="s">
         <v>243</v>
       </c>
-      <c r="E16" s="120"/>
+      <c r="E16" s="124"/>
       <c r="F16" s="46" t="s">
         <v>95</v>
       </c>
@@ -6862,22 +6862,22 @@
       <c r="H16" s="25"/>
     </row>
     <row r="17" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="113" t="s">
+      <c r="A17" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115" t="s">
+      <c r="B17" s="118"/>
+      <c r="C17" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="116"/>
+      <c r="D17" s="120"/>
       <c r="E17" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="117">
+      <c r="F17" s="121">
         <v>46227</v>
       </c>
-      <c r="G17" s="118"/>
-      <c r="H17" s="119"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -6929,18 +6929,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
       <c r="D1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="85" t="s">
+      <c r="E1" s="89" t="s">
         <v>132</v>
       </c>
-      <c r="F1" s="85"/>
+      <c r="F1" s="89"/>
     </row>
     <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="33"/>
@@ -6950,18 +6950,18 @@
       <c r="E2" s="34"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="85" t="s">
+      <c r="A3" s="89" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="85"/>
+      <c r="B3" s="89"/>
       <c r="C3" s="31"/>
       <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="85" t="s">
+      <c r="E3" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="85"/>
+      <c r="F3" s="89"/>
     </row>
     <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
@@ -6971,44 +6971,44 @@
       <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="78" t="s">
+      <c r="B5" s="87"/>
+      <c r="C5" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
     </row>
     <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="78" t="s">
+      <c r="B6" s="87"/>
+      <c r="C6" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
     </row>
     <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="78" t="s">
+      <c r="B7" s="87"/>
+      <c r="C7" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
     </row>
     <row r="8" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="79"/>
-      <c r="B8" s="79"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
+      <c r="A8" s="83"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
     </row>
     <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="32"/>
@@ -7018,19 +7018,19 @@
       <c r="E9" s="32"/>
     </row>
     <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="81"/>
-      <c r="C10" s="81"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
       <c r="D10" s="14"/>
       <c r="E10" s="32"/>
     </row>
     <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="82" t="s">
+      <c r="A11" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="82"/>
+      <c r="B11" s="86"/>
       <c r="C11" s="45" t="s">
         <v>95</v>
       </c>
@@ -7038,10 +7038,10 @@
       <c r="E11" s="32"/>
     </row>
     <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="82" t="s">
+      <c r="A12" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="82"/>
+      <c r="B12" s="86"/>
       <c r="C12" s="45" t="s">
         <v>95</v>
       </c>
@@ -7049,10 +7049,10 @@
       <c r="E12" s="32"/>
     </row>
     <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="82" t="s">
+      <c r="A13" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="82"/>
+      <c r="B13" s="86"/>
       <c r="C13" s="45" t="s">
         <v>95</v>
       </c>
@@ -7060,10 +7060,10 @@
       <c r="E13" s="32"/>
     </row>
     <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="91" t="s">
+      <c r="A14" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="90"/>
+      <c r="B14" s="94"/>
       <c r="C14" s="45" t="s">
         <v>95</v>
       </c>
@@ -7071,10 +7071,10 @@
       <c r="E14" s="32"/>
     </row>
     <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="82" t="s">
+      <c r="A15" s="86" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="82"/>
+      <c r="B15" s="86"/>
       <c r="C15" s="45" t="s">
         <v>95</v>
       </c>
@@ -7082,10 +7082,10 @@
       <c r="E15" s="32"/>
     </row>
     <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="82" t="s">
+      <c r="A16" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="82"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="45" t="s">
         <v>95</v>
       </c>
@@ -7140,94 +7140,94 @@
       <c r="C1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="97" t="s">
+      <c r="D1" s="101" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="99"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="103"/>
     </row>
     <row r="2" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="100" t="s">
+      <c r="B2" s="104" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="101"/>
+      <c r="C2" s="105"/>
       <c r="D2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="100" t="s">
+      <c r="E2" s="104" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="103"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="107"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="104" t="s">
+      <c r="A3" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="99"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="103"/>
     </row>
     <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="19">
         <v>1</v>
       </c>
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="98" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="96"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="100"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>2</v>
       </c>
-      <c r="B5" s="100" t="s">
+      <c r="B5" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="103"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="107"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="106" t="s">
+      <c r="A6" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="99"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="103"/>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="95"/>
-      <c r="C7" s="112"/>
-      <c r="D7" s="131" t="s">
+      <c r="B7" s="99"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="135" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="112"/>
+      <c r="E7" s="116"/>
       <c r="F7" s="21" t="s">
         <v>20</v>
       </c>
@@ -7242,14 +7242,14 @@
       <c r="A8" s="19">
         <v>1</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="98" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="111"/>
-      <c r="D8" s="94" t="s">
+      <c r="C8" s="115"/>
+      <c r="D8" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E8" s="112"/>
+      <c r="E8" s="116"/>
       <c r="F8" s="46" t="s">
         <v>95</v>
       </c>
@@ -7260,14 +7260,14 @@
       <c r="A9" s="19">
         <v>2</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="98" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="94" t="s">
+      <c r="C9" s="115"/>
+      <c r="D9" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E9" s="112"/>
+      <c r="E9" s="116"/>
       <c r="F9" s="46" t="s">
         <v>95</v>
       </c>
@@ -7278,14 +7278,14 @@
       <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="94" t="s">
+      <c r="B10" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="94" t="s">
+      <c r="C10" s="115"/>
+      <c r="D10" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E10" s="112"/>
+      <c r="E10" s="116"/>
       <c r="F10" s="46" t="s">
         <v>95</v>
       </c>
@@ -7296,14 +7296,14 @@
       <c r="A11" s="19">
         <v>4</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="111"/>
-      <c r="D11" s="94" t="s">
+      <c r="C11" s="115"/>
+      <c r="D11" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E11" s="112"/>
+      <c r="E11" s="116"/>
       <c r="F11" s="46" t="s">
         <v>95</v>
       </c>
@@ -7314,14 +7314,14 @@
       <c r="A12" s="19">
         <v>5</v>
       </c>
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="111"/>
-      <c r="D12" s="94" t="s">
+      <c r="C12" s="115"/>
+      <c r="D12" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E12" s="112"/>
+      <c r="E12" s="116"/>
       <c r="F12" s="46" t="s">
         <v>95</v>
       </c>
@@ -7332,14 +7332,14 @@
       <c r="A13" s="19">
         <v>6</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="111"/>
-      <c r="D13" s="94" t="s">
+      <c r="C13" s="115"/>
+      <c r="D13" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E13" s="112"/>
+      <c r="E13" s="116"/>
       <c r="F13" s="46" t="s">
         <v>95</v>
       </c>
@@ -7350,14 +7350,14 @@
       <c r="A14" s="23">
         <v>7</v>
       </c>
-      <c r="B14" s="94" t="s">
+      <c r="B14" s="98" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="111"/>
-      <c r="D14" s="94" t="s">
+      <c r="C14" s="115"/>
+      <c r="D14" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E14" s="112"/>
+      <c r="E14" s="116"/>
       <c r="F14" s="46" t="s">
         <v>95</v>
       </c>
@@ -7368,14 +7368,14 @@
       <c r="A15" s="23">
         <v>8</v>
       </c>
-      <c r="B15" s="94" t="s">
+      <c r="B15" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="111"/>
-      <c r="D15" s="94" t="s">
+      <c r="C15" s="115"/>
+      <c r="D15" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E15" s="112"/>
+      <c r="E15" s="116"/>
       <c r="F15" s="46" t="s">
         <v>95</v>
       </c>
@@ -7386,14 +7386,14 @@
       <c r="A16" s="23">
         <v>9</v>
       </c>
-      <c r="B16" s="100" t="s">
+      <c r="B16" s="104" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="120"/>
-      <c r="D16" s="94" t="s">
+      <c r="C16" s="124"/>
+      <c r="D16" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="E16" s="112"/>
+      <c r="E16" s="116"/>
       <c r="F16" s="46" t="s">
         <v>95</v>
       </c>
@@ -7401,22 +7401,22 @@
       <c r="H16" s="25"/>
     </row>
     <row r="17" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="113" t="s">
+      <c r="A17" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115" t="s">
+      <c r="B17" s="118"/>
+      <c r="C17" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="116"/>
+      <c r="D17" s="120"/>
       <c r="E17" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="134">
+      <c r="F17" s="138">
         <v>46227</v>
       </c>
-      <c r="G17" s="135"/>
-      <c r="H17" s="136"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="140"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
@@ -7480,92 +7480,92 @@
       <c r="C1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="97" t="s">
+      <c r="D1" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="99"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="103"/>
     </row>
     <row r="2" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="100" t="s">
+      <c r="B2" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="101"/>
+      <c r="C2" s="105"/>
       <c r="D2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="100" t="s">
+      <c r="E2" s="104" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="103"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="107"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="104" t="s">
+      <c r="A3" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="99"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="103"/>
     </row>
     <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="19">
         <v>1</v>
       </c>
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="98" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="96"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="100"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>2</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="103"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="107"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="106" t="s">
+      <c r="A6" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="99"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="103"/>
     </row>
     <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.35">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="95"/>
-      <c r="C7" s="112"/>
-      <c r="D7" s="131" t="s">
+      <c r="B7" s="99"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="135" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="112"/>
+      <c r="E7" s="116"/>
       <c r="F7" s="21" t="s">
         <v>20</v>
       </c>
@@ -7580,14 +7580,14 @@
       <c r="A8" s="19">
         <v>1</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="98" t="s">
         <v>232</v>
       </c>
-      <c r="C8" s="112"/>
-      <c r="D8" s="94" t="s">
+      <c r="C8" s="116"/>
+      <c r="D8" s="98" t="s">
         <v>236</v>
       </c>
-      <c r="E8" s="112"/>
+      <c r="E8" s="116"/>
       <c r="F8" s="46" t="s">
         <v>95</v>
       </c>
@@ -7598,14 +7598,14 @@
       <c r="A9" s="19">
         <v>2</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="98" t="s">
         <v>233</v>
       </c>
-      <c r="C9" s="112"/>
-      <c r="D9" s="94" t="s">
+      <c r="C9" s="116"/>
+      <c r="D9" s="98" t="s">
         <v>237</v>
       </c>
-      <c r="E9" s="112"/>
+      <c r="E9" s="116"/>
       <c r="F9" s="46" t="s">
         <v>95</v>
       </c>
@@ -7616,14 +7616,14 @@
       <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="94" t="s">
+      <c r="B10" s="98" t="s">
         <v>234</v>
       </c>
-      <c r="C10" s="112"/>
-      <c r="D10" s="94" t="s">
+      <c r="C10" s="116"/>
+      <c r="D10" s="98" t="s">
         <v>236</v>
       </c>
-      <c r="E10" s="112"/>
+      <c r="E10" s="116"/>
       <c r="F10" s="46" t="s">
         <v>95</v>
       </c>
@@ -7634,14 +7634,14 @@
       <c r="A11" s="19">
         <v>4</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="98" t="s">
         <v>235</v>
       </c>
-      <c r="C11" s="112"/>
-      <c r="D11" s="94" t="s">
+      <c r="C11" s="116"/>
+      <c r="D11" s="98" t="s">
         <v>238</v>
       </c>
-      <c r="E11" s="112"/>
+      <c r="E11" s="116"/>
       <c r="F11" s="46" t="s">
         <v>95</v>
       </c>
@@ -7652,10 +7652,10 @@
       <c r="A12" s="19">
         <v>5</v>
       </c>
-      <c r="B12" s="94"/>
-      <c r="C12" s="112"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="112"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="116"/>
       <c r="F12" s="21"/>
       <c r="G12" s="21"/>
       <c r="H12" s="22"/>
@@ -7664,10 +7664,10 @@
       <c r="A13" s="19">
         <v>6</v>
       </c>
-      <c r="B13" s="94"/>
-      <c r="C13" s="112"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="112"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="116"/>
       <c r="F13" s="21"/>
       <c r="G13" s="21"/>
       <c r="H13" s="22"/>
@@ -7676,31 +7676,31 @@
       <c r="A14" s="23">
         <v>7</v>
       </c>
-      <c r="B14" s="132"/>
-      <c r="C14" s="133"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="133"/>
+      <c r="B14" s="136"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="136"/>
+      <c r="E14" s="137"/>
       <c r="F14" s="24"/>
       <c r="G14" s="24"/>
       <c r="H14" s="25"/>
     </row>
     <row r="15" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="113" t="s">
+      <c r="A15" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="114"/>
-      <c r="C15" s="115" t="s">
+      <c r="B15" s="118"/>
+      <c r="C15" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="116"/>
+      <c r="D15" s="120"/>
       <c r="E15" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="137">
+      <c r="F15" s="141">
         <v>46228</v>
       </c>
-      <c r="G15" s="138"/>
-      <c r="H15" s="139"/>
+      <c r="G15" s="142"/>
+      <c r="H15" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="27">

--- a/04_Yetkili_Kullanıcı_Profile_Settings/4 - AU - PS.xlsx
+++ b/04_Yetkili_Kullanıcı_Profile_Settings/4 - AU - PS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bovay\Desktop\¨¨¨¨¨¨\PROJECTS\CV TASLAK\POWER PULSE - PROJE\PLANLAMA\04 - YETKİLİ KULLANICI - PROFİL AYARLARI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2869CDED-F9B7-45FA-BD1C-72F5A701652F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0131B530-5455-4EFE-9C97-C788F8C3A578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="12090" firstSheet="9" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4. GEREKSİNİM TAKİP MATRİSİ" sheetId="11" r:id="rId1"/>
@@ -539,9 +539,6 @@
     <t>CL - 008 [AU - PS]</t>
   </si>
   <si>
-    <t xml:space="preserve">CL - 009 [AU - PS] </t>
-  </si>
-  <si>
     <t>TC - 014 [AU - PS]</t>
   </si>
   <si>
@@ -992,6 +989,9 @@
   </si>
   <si>
     <t>UserForm verileri backend'deki verilerden farklı olduğunda Save butonu aktif duruma gelmelidir.</t>
+  </si>
+  <si>
+    <t>CL - 009[AU - PS]</t>
   </si>
 </sst>
 </file>
@@ -1924,6 +1924,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1935,30 +1959,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1968,84 +1968,84 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="10" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2060,45 +2060,45 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2488,10 +2488,10 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="57" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C1" s="78"/>
       <c r="D1" s="78"/>
@@ -2499,14 +2499,14 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="57" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C2" s="78"/>
       <c r="F2" s="59" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G2" s="58" t="s">
         <v>2</v>
@@ -2515,15 +2515,15 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="57" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B3" s="79" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C3" s="78"/>
       <c r="D3" s="78"/>
       <c r="F3" s="59" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G3" s="61">
         <v>46227</v>
@@ -2532,17 +2532,17 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="57" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B4" s="80" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C4" s="80"/>
       <c r="F4" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="62" t="s">
         <v>142</v>
-      </c>
-      <c r="G4" s="62" t="s">
-        <v>143</v>
       </c>
       <c r="H4" s="58"/>
     </row>
@@ -2552,2004 +2552,2004 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="63" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="63" t="s">
+      <c r="C7" s="65" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="C7" s="65" t="s">
+      <c r="E7" s="63" t="s">
+        <v>146</v>
+      </c>
+      <c r="F7" s="63" t="s">
+        <v>147</v>
+      </c>
+      <c r="G7" s="63" t="s">
+        <v>148</v>
+      </c>
+      <c r="H7" s="65" t="s">
         <v>150</v>
-      </c>
-      <c r="D7" s="63" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" s="63" t="s">
-        <v>147</v>
-      </c>
-      <c r="F7" s="63" t="s">
-        <v>148</v>
-      </c>
-      <c r="G7" s="63" t="s">
-        <v>149</v>
-      </c>
-      <c r="H7" s="65" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="73" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B8" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D8" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E8" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F8" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F8" s="64" t="s">
+      <c r="G8" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H8" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G8" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H8" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="73" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B9" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D9" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E9" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F9" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F9" s="64" t="s">
+      <c r="G9" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H9" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G9" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H9" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="73" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D10" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E10" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F10" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F10" s="64" t="s">
+      <c r="G10" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H10" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G10" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H10" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="73" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B11" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D11" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F11" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F11" s="64" t="s">
+      <c r="G11" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H11" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G11" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H11" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="73" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B12" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D12" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E12" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F12" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F12" s="64" t="s">
+      <c r="G12" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H12" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G12" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H12" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="73" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B13" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D13" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E13" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F13" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F13" s="64" t="s">
+      <c r="G13" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H13" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G13" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H13" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="73" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B14" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C14" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D14" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F14" s="64" t="s">
+      <c r="G14" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H14" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G14" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H14" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="73" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B15" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D15" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E15" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F15" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F15" s="64" t="s">
+      <c r="G15" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H15" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G15" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H15" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="77" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="73" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B16" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D16" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E16" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F16" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F16" s="64" t="s">
+      <c r="G16" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H16" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G16" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H16" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="73" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B17" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D17" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E17" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F17" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F17" s="64" t="s">
+      <c r="G17" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H17" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G17" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H17" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="73" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B18" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" s="64" t="s">
         <v>165</v>
-      </c>
-      <c r="C18" s="64" t="s">
-        <v>166</v>
       </c>
       <c r="D18" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E18" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F18" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F18" s="64" t="s">
+      <c r="G18" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H18" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G18" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H18" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="73" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B19" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D19" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E19" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F19" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F19" s="64" t="s">
+      <c r="G19" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H19" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G19" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H19" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="98" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="73" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B20" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D20" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E20" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F20" s="64" t="s">
+      <c r="G20" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H20" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G20" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H20" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="88" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="73" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B21" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D21" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E21" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F21" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F21" s="64" t="s">
+      <c r="G21" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G21" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H21" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="73" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B22" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="64" t="s">
         <v>165</v>
-      </c>
-      <c r="C22" s="64" t="s">
-        <v>166</v>
       </c>
       <c r="D22" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E22" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F22" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F22" s="64" t="s">
+      <c r="G22" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H22" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G22" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H22" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="63.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="73" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B23" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D23" s="64" t="s">
         <v>128</v>
       </c>
       <c r="E23" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F23" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F23" s="64" t="s">
+      <c r="G23" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H23" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G23" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H23" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="88.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="73" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B24" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D24" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E24" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F24" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F24" s="64" t="s">
+      <c r="G24" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H24" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G24" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H24" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="88" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="73" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B25" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D25" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E25" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F25" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F25" s="64" t="s">
+      <c r="G25" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H25" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G25" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H25" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="73" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B26" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D26" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E26" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F26" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F26" s="64" t="s">
+      <c r="G26" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H26" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G26" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H26" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="78.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="73" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B27" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D27" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E27" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F27" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F27" s="64" t="s">
+      <c r="G27" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H27" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G27" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H27" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="83.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B28" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D28" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E28" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F28" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F28" s="64" t="s">
+      <c r="G28" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H28" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G28" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H28" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="90.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="73" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B29" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D29" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E29" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F29" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F29" s="64" t="s">
+      <c r="G29" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H29" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G29" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H29" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="81.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="73" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B30" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E30" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F30" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F30" s="64" t="s">
+      <c r="G30" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H30" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G30" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H30" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="73" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B31" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D31" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E31" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F31" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F31" s="64" t="s">
+      <c r="G31" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H31" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G31" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H31" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="102" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="73" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B32" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C32" s="64" t="s">
+        <v>170</v>
+      </c>
+      <c r="D32" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E32" s="64" t="s">
+        <v>129</v>
+      </c>
+      <c r="F32" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="D32" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="E32" s="64" t="s">
-        <v>130</v>
-      </c>
-      <c r="F32" s="64" t="s">
+      <c r="G32" s="64" t="s">
+        <v>151</v>
+      </c>
+      <c r="H32" s="64" t="s">
         <v>172</v>
-      </c>
-      <c r="G32" s="64" t="s">
-        <v>152</v>
-      </c>
-      <c r="H32" s="64" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="93" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="73" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B33" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C33" s="64" t="s">
+        <v>170</v>
+      </c>
+      <c r="D33" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E33" s="64" t="s">
+        <v>129</v>
+      </c>
+      <c r="F33" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="D33" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="E33" s="64" t="s">
-        <v>130</v>
-      </c>
-      <c r="F33" s="64" t="s">
+      <c r="G33" s="64" t="s">
+        <v>151</v>
+      </c>
+      <c r="H33" s="64" t="s">
         <v>172</v>
-      </c>
-      <c r="G33" s="64" t="s">
-        <v>152</v>
-      </c>
-      <c r="H33" s="64" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="73" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B34" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D34" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E34" s="64" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E34" s="64" t="s">
-        <v>130</v>
-      </c>
-      <c r="F34" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G34" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H34" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="82" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="73" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B35" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D35" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E35" s="64" t="s">
+        <v>129</v>
+      </c>
+      <c r="F35" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E35" s="64" t="s">
-        <v>130</v>
-      </c>
-      <c r="F35" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G35" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H35" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="78.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="73" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B36" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D36" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E36" s="64" t="s">
+        <v>129</v>
+      </c>
+      <c r="F36" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E36" s="64" t="s">
-        <v>130</v>
-      </c>
-      <c r="F36" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G36" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H36" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="88" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="73" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B37" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D37" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E37" s="64" t="s">
+        <v>129</v>
+      </c>
+      <c r="F37" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E37" s="64" t="s">
-        <v>130</v>
-      </c>
-      <c r="F37" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G37" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H37" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="82" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="73" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B38" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D38" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E38" s="64" t="s">
+        <v>129</v>
+      </c>
+      <c r="F38" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E38" s="64" t="s">
-        <v>130</v>
-      </c>
-      <c r="F38" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G38" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H38" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="106" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="73" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B39" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D39" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E39" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="F39" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E39" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="F39" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G39" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H39" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="119.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="73" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B40" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D40" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E40" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="F40" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E40" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="F40" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G40" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H40" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="84" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="73" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B41" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D41" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E41" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="F41" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E41" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="F41" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G41" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H41" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="73" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B42" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D42" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E42" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="F42" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E42" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="F42" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G42" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H42" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="106" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="73" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B43" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D43" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E43" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="F43" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E43" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="F43" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G43" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H43" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="88.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="73" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B44" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D44" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E44" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="F44" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E44" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="F44" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G44" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H44" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="114.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="73" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B45" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D45" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E45" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="F45" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E45" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="F45" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G45" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H45" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="97.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B46" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D46" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E46" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="F46" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E46" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="F46" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G46" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H46" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="73" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B47" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D47" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E47" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="F47" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E47" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="F47" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G47" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H47" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="73" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B48" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D48" s="64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E48" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F48" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F48" s="64" t="s">
+      <c r="G48" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H48" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G48" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H48" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="73" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B49" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D49" s="64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E49" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F49" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F49" s="64" t="s">
+      <c r="G49" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H49" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G49" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H49" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="73" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B50" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D50" s="64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E50" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F50" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F50" s="64" t="s">
+      <c r="G50" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H50" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G50" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H50" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="77" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="73" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B51" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D51" s="64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E51" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F51" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F51" s="64" t="s">
+      <c r="G51" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H51" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G51" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H51" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="67" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="73" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B52" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D52" s="64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E52" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F52" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F52" s="64" t="s">
+      <c r="G52" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H52" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G52" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H52" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="73" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B53" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D53" s="64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E53" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F53" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F53" s="64" t="s">
+      <c r="G53" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H53" s="64" t="s">
         <v>168</v>
-      </c>
-      <c r="G53" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="H53" s="64" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="86" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B54" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D54" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E54" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="F54" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E54" s="64" t="s">
-        <v>133</v>
-      </c>
-      <c r="F54" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G54" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H54" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="73" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B55" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D55" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E55" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="F55" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E55" s="64" t="s">
-        <v>133</v>
-      </c>
-      <c r="F55" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G55" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H55" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="71" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="73" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B56" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D56" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E56" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="F56" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E56" s="64" t="s">
-        <v>133</v>
-      </c>
-      <c r="F56" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G56" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H56" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="73" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B57" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D57" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E57" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="F57" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E57" s="64" t="s">
-        <v>133</v>
-      </c>
-      <c r="F57" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G57" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H57" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B58" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D58" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E58" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="F58" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E58" s="64" t="s">
-        <v>133</v>
-      </c>
-      <c r="F58" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G58" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H58" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="77" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="73" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B59" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D59" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E59" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="F59" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E59" s="64" t="s">
-        <v>133</v>
-      </c>
-      <c r="F59" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G59" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H59" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="71.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="73" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B60" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D60" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E60" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="F60" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E60" s="64" t="s">
-        <v>133</v>
-      </c>
-      <c r="F60" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G60" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H60" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="77" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="73" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B61" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D61" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E61" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="F61" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E61" s="64" t="s">
-        <v>133</v>
-      </c>
-      <c r="F61" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G61" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H61" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="78" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="73" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B62" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D62" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E62" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="F62" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E62" s="64" t="s">
-        <v>133</v>
-      </c>
-      <c r="F62" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G62" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H62" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="111" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="73" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B63" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D63" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E63" s="64" t="s">
+        <v>133</v>
+      </c>
+      <c r="F63" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E63" s="64" t="s">
-        <v>134</v>
-      </c>
-      <c r="F63" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G63" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H63" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="111.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="73" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B64" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D64" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E64" s="64" t="s">
+        <v>133</v>
+      </c>
+      <c r="F64" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E64" s="64" t="s">
-        <v>134</v>
-      </c>
-      <c r="F64" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G64" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H64" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="73" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B65" s="64" t="s">
         <v>97</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D65" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="E65" s="64" t="s">
+        <v>133</v>
+      </c>
+      <c r="F65" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E65" s="64" t="s">
-        <v>134</v>
-      </c>
-      <c r="F65" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G65" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H65" s="64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="116.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="75" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B66" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C66" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C66" s="64" t="s">
-        <v>166</v>
-      </c>
       <c r="D66" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E66" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F66" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F66" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G66" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H66" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="117" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B67" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C67" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C67" s="64" t="s">
-        <v>166</v>
-      </c>
       <c r="D67" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E67" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F67" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F67" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G67" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H67" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="105.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="76" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B68" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C68" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C68" s="64" t="s">
-        <v>166</v>
-      </c>
       <c r="D68" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E68" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F68" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F68" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G68" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H68" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="107.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="73" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B69" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C69" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C69" s="64" t="s">
-        <v>166</v>
-      </c>
       <c r="D69" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E69" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F69" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F69" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G69" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H69" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="103" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="73" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B70" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C70" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C70" s="64" t="s">
-        <v>166</v>
-      </c>
       <c r="D70" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E70" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F70" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F70" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G70" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H70" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="91.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="73" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B71" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C71" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C71" s="64" t="s">
-        <v>166</v>
-      </c>
       <c r="D71" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E71" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F71" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F71" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G71" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H71" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="73" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B72" s="56" t="s">
         <v>97</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D72" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E72" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F72" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F72" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G72" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H72" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="102.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="73" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B73" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C73" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C73" s="64" t="s">
-        <v>166</v>
-      </c>
       <c r="D73" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E73" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F73" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F73" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G73" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H73" s="64" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="106" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="73" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B74" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C74" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C74" s="64" t="s">
-        <v>166</v>
-      </c>
       <c r="D74" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E74" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F74" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F74" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G74" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H74" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="110.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="73" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B75" s="56" t="s">
         <v>97</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D75" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E75" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F75" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F75" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G75" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H75" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="73" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B76" s="56" t="s">
         <v>97</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D76" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E76" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F76" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F76" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G76" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H76" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="102" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="73" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B77" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C77" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C77" s="64" t="s">
-        <v>166</v>
-      </c>
       <c r="D77" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E77" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F77" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F77" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G77" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H77" s="64" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="100.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="73" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B78" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C78" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C78" s="64" t="s">
-        <v>166</v>
-      </c>
       <c r="D78" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E78" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F78" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F78" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G78" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H78" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="94.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="73" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B79" s="56" t="s">
         <v>97</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D79" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E79" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F79" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F79" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G79" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H79" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="73" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B80" s="56" t="s">
         <v>97</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D80" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E80" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F80" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F80" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G80" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H80" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="96.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="73" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B81" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C81" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C81" s="64" t="s">
-        <v>166</v>
-      </c>
       <c r="D81" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E81" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F81" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F81" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G81" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H81" s="64" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="117.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="73" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B82" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C82" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="64" t="s">
-        <v>166</v>
-      </c>
       <c r="D82" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E82" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F82" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F82" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G82" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H82" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="109" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="73" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B83" s="56" t="s">
         <v>97</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D83" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E83" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="F83" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="F83" s="64" t="s">
-        <v>168</v>
-      </c>
       <c r="G83" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H83" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
@@ -4587,25 +4587,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
       <c r="K1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="89" t="s">
-        <v>135</v>
-      </c>
-      <c r="M1" s="89"/>
+      <c r="L1" s="88" t="s">
+        <v>134</v>
+      </c>
+      <c r="M1" s="88"/>
     </row>
     <row r="2" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="35"/>
@@ -4622,10 +4622,10 @@
       <c r="L2" s="36"/>
     </row>
     <row r="3" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="89" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="89"/>
+      <c r="A3" s="88" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="88"/>
       <c r="C3" s="36"/>
       <c r="D3" s="36"/>
       <c r="E3" s="53"/>
@@ -4637,10 +4637,10 @@
       <c r="K3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="89" t="s">
+      <c r="L3" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="89"/>
+      <c r="M3" s="88"/>
     </row>
     <row r="4" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
@@ -4657,62 +4657,62 @@
       <c r="L4" s="7"/>
     </row>
     <row r="5" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="87" t="s">
+      <c r="A5" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="82" t="s">
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
     </row>
     <row r="6" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="87"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="87"/>
-      <c r="E6" s="87"/>
-      <c r="F6" s="87"/>
-      <c r="G6" s="87"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="87"/>
-      <c r="J6" s="82" t="s">
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
+      <c r="K6" s="90"/>
+      <c r="L6" s="90"/>
     </row>
     <row r="7" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="87"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="82" t="s">
+      <c r="B7" s="89"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
+      <c r="E7" s="89"/>
+      <c r="F7" s="89"/>
+      <c r="G7" s="89"/>
+      <c r="H7" s="89"/>
+      <c r="I7" s="89"/>
+      <c r="J7" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
+      <c r="K7" s="90"/>
+      <c r="L7" s="90"/>
     </row>
     <row r="8" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="83"/>
-      <c r="B8" s="83"/>
+      <c r="A8" s="91"/>
+      <c r="B8" s="91"/>
       <c r="C8" s="39"/>
       <c r="D8" s="39"/>
       <c r="E8" s="54"/>
@@ -4720,9 +4720,9 @@
       <c r="G8" s="54"/>
       <c r="H8" s="54"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="84"/>
-      <c r="K8" s="84"/>
-      <c r="L8" s="84"/>
+      <c r="J8" s="92"/>
+      <c r="K8" s="92"/>
+      <c r="L8" s="92"/>
     </row>
     <row r="9" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="40"/>
@@ -4739,26 +4739,26 @@
       <c r="L9" s="40"/>
     </row>
     <row r="10" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="85"/>
-      <c r="J10" s="85"/>
-      <c r="K10" s="85"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="93"/>
+      <c r="K10" s="93"/>
       <c r="L10" s="40"/>
     </row>
     <row r="11" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="147" t="s">
+      <c r="A11" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="148"/>
+      <c r="B11" s="150"/>
       <c r="C11" s="66" t="s">
         <v>75</v>
       </c>
@@ -4771,21 +4771,21 @@
       <c r="F11" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="146" t="s">
+      <c r="G11" s="157" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="146"/>
-      <c r="I11" s="146" t="s">
+      <c r="H11" s="157"/>
+      <c r="I11" s="157" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="146"/>
+      <c r="J11" s="157"/>
       <c r="K11" s="67" t="s">
         <v>83</v>
       </c>
       <c r="L11" s="40"/>
     </row>
     <row r="12" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="149" t="s">
+      <c r="A12" s="151" t="s">
         <v>92</v>
       </c>
       <c r="B12" s="41" t="s">
@@ -4797,17 +4797,17 @@
       </c>
       <c r="E12" s="41"/>
       <c r="F12" s="42"/>
-      <c r="G12" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="H12" s="144"/>
-      <c r="I12" s="145"/>
-      <c r="J12" s="145"/>
+      <c r="G12" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="148"/>
+      <c r="I12" s="158"/>
+      <c r="J12" s="158"/>
       <c r="K12" s="68"/>
       <c r="L12" s="40"/>
     </row>
     <row r="13" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="151"/>
+      <c r="A13" s="153"/>
       <c r="B13" s="41" t="s">
         <v>81</v>
       </c>
@@ -4817,17 +4817,17 @@
       <c r="D13" s="41"/>
       <c r="E13" s="41"/>
       <c r="F13" s="42"/>
-      <c r="G13" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="H13" s="144"/>
-      <c r="I13" s="145"/>
-      <c r="J13" s="145"/>
+      <c r="G13" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13" s="148"/>
+      <c r="I13" s="158"/>
+      <c r="J13" s="158"/>
       <c r="K13" s="68"/>
       <c r="L13" s="40"/>
     </row>
     <row r="14" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="152" t="s">
+      <c r="A14" s="154" t="s">
         <v>93</v>
       </c>
       <c r="B14" s="41" t="s">
@@ -4839,17 +4839,17 @@
       </c>
       <c r="E14" s="41"/>
       <c r="F14" s="42"/>
-      <c r="G14" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="H14" s="144"/>
-      <c r="I14" s="145"/>
-      <c r="J14" s="145"/>
+      <c r="G14" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="148"/>
+      <c r="I14" s="158"/>
+      <c r="J14" s="158"/>
       <c r="K14" s="68"/>
       <c r="L14" s="40"/>
     </row>
     <row r="15" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="154"/>
+      <c r="A15" s="156"/>
       <c r="B15" s="41" t="s">
         <v>81</v>
       </c>
@@ -4859,17 +4859,17 @@
       <c r="D15" s="43"/>
       <c r="E15" s="43"/>
       <c r="F15" s="42"/>
-      <c r="G15" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="H15" s="144"/>
-      <c r="I15" s="145"/>
-      <c r="J15" s="145"/>
+      <c r="G15" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="148"/>
+      <c r="I15" s="158"/>
+      <c r="J15" s="158"/>
       <c r="K15" s="68"/>
       <c r="L15" s="40"/>
     </row>
     <row r="16" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="149" t="s">
+      <c r="A16" s="151" t="s">
         <v>94</v>
       </c>
       <c r="B16" s="41" t="s">
@@ -4881,17 +4881,17 @@
       <c r="F16" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="G16" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="H16" s="144"/>
-      <c r="I16" s="145"/>
-      <c r="J16" s="145"/>
+      <c r="G16" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" s="148"/>
+      <c r="I16" s="158"/>
+      <c r="J16" s="158"/>
       <c r="K16" s="68"/>
       <c r="L16" s="40"/>
     </row>
     <row r="17" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="151"/>
+      <c r="A17" s="153"/>
       <c r="B17" s="41" t="s">
         <v>81</v>
       </c>
@@ -4901,12 +4901,12 @@
         <v>95</v>
       </c>
       <c r="F17" s="42"/>
-      <c r="G17" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="H17" s="144"/>
-      <c r="I17" s="145"/>
-      <c r="J17" s="145"/>
+      <c r="G17" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="148"/>
+      <c r="I17" s="158"/>
+      <c r="J17" s="158"/>
       <c r="K17" s="68"/>
       <c r="L17" s="40"/>
     </row>
@@ -4919,256 +4919,301 @@
         <v>91</v>
       </c>
       <c r="D18" s="97"/>
-      <c r="E18" s="85" t="s">
+      <c r="E18" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85" t="s">
+      <c r="F18" s="93"/>
+      <c r="G18" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="85"/>
+      <c r="H18" s="93"/>
       <c r="I18" s="96" t="s">
         <v>83</v>
       </c>
       <c r="J18" s="97"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19" s="149" t="s">
+      <c r="A19" s="151" t="s">
         <v>88</v>
       </c>
       <c r="B19" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="155" t="s">
+      <c r="C19" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="156"/>
-      <c r="E19" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" s="144"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="94"/>
+      <c r="D19" s="145"/>
+      <c r="E19" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" s="148"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="86"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20" s="150"/>
+      <c r="A20" s="152"/>
       <c r="B20" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="155" t="s">
+      <c r="C20" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="156"/>
-      <c r="E20" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="F20" s="144"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="93"/>
-      <c r="J20" s="94"/>
+      <c r="D20" s="145"/>
+      <c r="E20" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="148"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="86"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21" s="150"/>
+      <c r="A21" s="152"/>
       <c r="B21" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="155" t="s">
+      <c r="C21" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="D21" s="156"/>
-      <c r="E21" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" s="144"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="85"/>
-      <c r="I21" s="93"/>
-      <c r="J21" s="94"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" s="148"/>
+      <c r="G21" s="93"/>
+      <c r="H21" s="93"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="86"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22" s="151"/>
+      <c r="A22" s="153"/>
       <c r="B22" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="155" t="s">
+      <c r="C22" s="144" t="s">
         <v>126</v>
       </c>
-      <c r="D22" s="156"/>
-      <c r="E22" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22" s="144"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
-      <c r="I22" s="93"/>
-      <c r="J22" s="94"/>
+      <c r="D22" s="145"/>
+      <c r="E22" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="148"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="86"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23" s="152" t="s">
+      <c r="A23" s="154" t="s">
         <v>89</v>
       </c>
       <c r="B23" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="155" t="s">
+      <c r="C23" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="D23" s="156"/>
-      <c r="E23" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="144"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="85"/>
-      <c r="I23" s="93"/>
-      <c r="J23" s="94"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="148"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="86"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24" s="153"/>
+      <c r="A24" s="155"/>
       <c r="B24" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="155" t="s">
+      <c r="C24" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="D24" s="156"/>
-      <c r="E24" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24" s="144"/>
-      <c r="G24" s="85"/>
-      <c r="H24" s="85"/>
-      <c r="I24" s="93"/>
-      <c r="J24" s="94"/>
+      <c r="D24" s="145"/>
+      <c r="E24" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" s="148"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="86"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25" s="153"/>
+      <c r="A25" s="155"/>
       <c r="B25" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="155" t="s">
+      <c r="C25" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="D25" s="156"/>
-      <c r="E25" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="144"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="93"/>
-      <c r="J25" s="94"/>
+      <c r="D25" s="145"/>
+      <c r="E25" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="148"/>
+      <c r="G25" s="93"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="85"/>
+      <c r="J25" s="86"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="154"/>
+      <c r="A26" s="156"/>
       <c r="B26" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="155" t="s">
+      <c r="C26" s="144" t="s">
         <v>126</v>
       </c>
-      <c r="D26" s="156"/>
-      <c r="E26" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" s="144"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="157"/>
-      <c r="J26" s="158"/>
+      <c r="D26" s="145"/>
+      <c r="E26" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" s="148"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="146"/>
+      <c r="J26" s="147"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27" s="149" t="s">
+      <c r="A27" s="151" t="s">
         <v>90</v>
       </c>
       <c r="B27" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="155" t="s">
+      <c r="C27" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="D27" s="156"/>
-      <c r="E27" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="F27" s="144"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="94"/>
+      <c r="D27" s="145"/>
+      <c r="E27" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="148"/>
+      <c r="G27" s="93"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="85"/>
+      <c r="J27" s="86"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28" s="150"/>
+      <c r="A28" s="152"/>
       <c r="B28" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="155" t="s">
+      <c r="C28" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="156"/>
-      <c r="E28" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="F28" s="144"/>
-      <c r="G28" s="85"/>
-      <c r="H28" s="85"/>
-      <c r="I28" s="93"/>
-      <c r="J28" s="94"/>
+      <c r="D28" s="145"/>
+      <c r="E28" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28" s="148"/>
+      <c r="G28" s="93"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="85"/>
+      <c r="J28" s="86"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29" s="150"/>
+      <c r="A29" s="152"/>
       <c r="B29" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="155" t="s">
+      <c r="C29" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="D29" s="156"/>
-      <c r="E29" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="F29" s="144"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="94"/>
+      <c r="D29" s="145"/>
+      <c r="E29" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="148"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="86"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30" s="151"/>
+      <c r="A30" s="153"/>
       <c r="B30" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="155" t="s">
+      <c r="C30" s="144" t="s">
         <v>126</v>
       </c>
-      <c r="D30" s="156"/>
-      <c r="E30" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="F30" s="144"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="93"/>
-      <c r="J30" s="94"/>
+      <c r="D30" s="145"/>
+      <c r="E30" s="148" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30" s="148"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="87">
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="I30:J30"/>
     <mergeCell ref="C29:D29"/>
@@ -5185,64 +5230,19 @@
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="J8:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5259,18 +5259,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="89" t="s">
-        <v>128</v>
-      </c>
-      <c r="F1" s="89"/>
+      <c r="E1" s="88" t="s">
+        <v>273</v>
+      </c>
+      <c r="F1" s="88"/>
     </row>
     <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
@@ -5280,18 +5280,18 @@
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="89" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="89"/>
+      <c r="A3" s="88" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="88"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="89" t="s">
+      <c r="E3" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="89"/>
+      <c r="F3" s="88"/>
     </row>
     <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
@@ -5301,44 +5301,44 @@
       <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="87" t="s">
+      <c r="A5" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="82" t="s">
+      <c r="B5" s="89"/>
+      <c r="C5" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
     </row>
     <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="87"/>
-      <c r="C6" s="82" t="s">
+      <c r="B6" s="89"/>
+      <c r="C6" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
     </row>
     <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="87"/>
-      <c r="C7" s="82" t="s">
+      <c r="B7" s="89"/>
+      <c r="C7" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
     </row>
     <row r="8" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="83"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="84"/>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
+      <c r="A8" s="91"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="92"/>
     </row>
     <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="8"/>
@@ -5348,19 +5348,19 @@
       <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
       <c r="D10" s="14"/>
       <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="86"/>
+      <c r="B11" s="94"/>
       <c r="C11" s="45" t="s">
         <v>95</v>
       </c>
@@ -5369,7 +5369,7 @@
     </row>
     <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="81" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B12" s="81"/>
       <c r="C12" s="45" t="s">
@@ -5380,7 +5380,7 @@
     </row>
     <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B13" s="81"/>
       <c r="C13" s="45" t="s">
@@ -5390,10 +5390,10 @@
       <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="92" t="s">
-        <v>200</v>
-      </c>
-      <c r="B14" s="91"/>
+      <c r="A14" s="84" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="83"/>
       <c r="C14" s="45" t="s">
         <v>95</v>
       </c>
@@ -5402,7 +5402,7 @@
     </row>
     <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B15" s="81"/>
       <c r="C15" s="45" t="s">
@@ -5413,7 +5413,7 @@
     </row>
     <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="81" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B16" s="81"/>
       <c r="C16" s="45" t="s">
@@ -5423,10 +5423,10 @@
       <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="90" t="s">
-        <v>203</v>
-      </c>
-      <c r="B17" s="91"/>
+      <c r="A17" s="82" t="s">
+        <v>202</v>
+      </c>
+      <c r="B17" s="83"/>
       <c r="C17" s="45" t="s">
         <v>95</v>
       </c>
@@ -5434,10 +5434,10 @@
       <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="90" t="s">
-        <v>204</v>
-      </c>
-      <c r="B18" s="91"/>
+      <c r="A18" s="82" t="s">
+        <v>203</v>
+      </c>
+      <c r="B18" s="83"/>
       <c r="C18" s="45" t="s">
         <v>95</v>
       </c>
@@ -5445,10 +5445,10 @@
       <c r="E18" s="8"/>
     </row>
     <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="90" t="s">
-        <v>205</v>
-      </c>
-      <c r="B19" s="91"/>
+      <c r="A19" s="82" t="s">
+        <v>204</v>
+      </c>
+      <c r="B19" s="83"/>
       <c r="C19" s="45" t="s">
         <v>95</v>
       </c>
@@ -5456,10 +5456,10 @@
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="93" t="s">
+      <c r="A20" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="94"/>
+      <c r="B20" s="86"/>
       <c r="C20" s="45" t="s">
         <v>95</v>
       </c>
@@ -5467,10 +5467,10 @@
       <c r="E20" s="12"/>
     </row>
     <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="91"/>
+      <c r="B21" s="83"/>
       <c r="C21" s="45" t="s">
         <v>95</v>
       </c>
@@ -5478,10 +5478,10 @@
       <c r="E21" s="12"/>
     </row>
     <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="91"/>
+      <c r="B22" s="83"/>
       <c r="C22" s="45" t="s">
         <v>95</v>
       </c>
@@ -5489,10 +5489,10 @@
       <c r="E22" s="12"/>
     </row>
     <row r="23" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="91"/>
+      <c r="B23" s="83"/>
       <c r="C23" s="45" t="s">
         <v>95</v>
       </c>
@@ -5500,10 +5500,10 @@
       <c r="E23" s="12"/>
     </row>
     <row r="24" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="90" t="s">
+      <c r="A24" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="91"/>
+      <c r="B24" s="83"/>
       <c r="C24" s="45" t="s">
         <v>95</v>
       </c>
@@ -5511,10 +5511,10 @@
       <c r="E24" s="12"/>
     </row>
     <row r="25" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="91"/>
+      <c r="B25" s="83"/>
       <c r="C25" s="45" t="s">
         <v>95</v>
       </c>
@@ -5522,10 +5522,10 @@
       <c r="E25" s="12"/>
     </row>
     <row r="26" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="90" t="s">
+      <c r="A26" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="91"/>
+      <c r="B26" s="83"/>
       <c r="C26" s="45" t="s">
         <v>95</v>
       </c>
@@ -5533,8 +5533,8 @@
       <c r="E26" s="12"/>
     </row>
     <row r="27" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="90"/>
-      <c r="B27" s="91"/>
+      <c r="A27" s="82"/>
+      <c r="B27" s="83"/>
       <c r="C27" s="15"/>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
@@ -5548,6 +5548,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E3:F3"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A19:B19"/>
@@ -5564,21 +5579,6 @@
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5597,19 +5597,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
       <c r="E1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="89" t="s">
-        <v>129</v>
-      </c>
-      <c r="G1" s="89"/>
+      <c r="F1" s="88" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
@@ -5620,19 +5620,19 @@
       <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="89" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="89"/>
+      <c r="A3" s="88" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="88"/>
       <c r="C3" s="4"/>
       <c r="D3" s="10"/>
       <c r="E3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="89" t="s">
+      <c r="F3" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="89"/>
+      <c r="G3" s="88"/>
     </row>
     <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
@@ -5643,48 +5643,48 @@
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="87" t="s">
+      <c r="A5" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="82" t="s">
+      <c r="B5" s="89"/>
+      <c r="C5" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
     </row>
     <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="87"/>
-      <c r="C6" s="82" t="s">
+      <c r="B6" s="89"/>
+      <c r="C6" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
     </row>
     <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="87"/>
-      <c r="C7" s="82" t="s">
+      <c r="B7" s="89"/>
+      <c r="C7" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
+      <c r="F7" s="90"/>
     </row>
     <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="83"/>
-      <c r="B8" s="83"/>
+      <c r="A8" s="91"/>
+      <c r="B8" s="91"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
     </row>
     <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
@@ -5711,26 +5711,26 @@
       <c r="F10" s="69"/>
     </row>
     <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="94" t="s">
+        <v>173</v>
+      </c>
+      <c r="B11" s="94"/>
+      <c r="C11" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="70"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="94" t="s">
         <v>174</v>
       </c>
-      <c r="B11" s="86"/>
-      <c r="C11" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F11" s="70"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="86" t="s">
-        <v>175</v>
-      </c>
-      <c r="B12" s="86"/>
+      <c r="B12" s="94"/>
       <c r="C12" s="45" t="s">
         <v>95</v>
       </c>
@@ -5744,89 +5744,89 @@
     </row>
     <row r="13" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="95" t="s">
+        <v>175</v>
+      </c>
+      <c r="B13" s="86"/>
+      <c r="C13" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" s="70"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="94" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="94"/>
-      <c r="C13" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F13" s="70"/>
-    </row>
-    <row r="14" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="86" t="s">
+      <c r="B14" s="94"/>
+      <c r="C14" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="70"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="94" t="s">
         <v>177</v>
       </c>
-      <c r="B14" s="86"/>
-      <c r="C14" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F14" s="70"/>
-    </row>
-    <row r="15" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="86" t="s">
+      <c r="B15" s="94"/>
+      <c r="C15" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="70"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="85" t="s">
         <v>178</v>
       </c>
-      <c r="B15" s="86"/>
-      <c r="C15" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" s="70"/>
-    </row>
-    <row r="16" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="93" t="s">
+      <c r="B16" s="86"/>
+      <c r="C16" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="70"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="85" t="s">
         <v>179</v>
       </c>
-      <c r="B16" s="94"/>
-      <c r="C16" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F16" s="70"/>
-    </row>
-    <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="93" t="s">
+      <c r="B17" s="86"/>
+      <c r="C17" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="70"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="85" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="94"/>
-      <c r="C17" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="D17" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F17" s="70"/>
-    </row>
-    <row r="18" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="93" t="s">
-        <v>181</v>
-      </c>
-      <c r="B18" s="94"/>
+      <c r="B18" s="86"/>
       <c r="C18" s="45" t="s">
         <v>95</v>
       </c>
@@ -5840,12 +5840,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
@@ -5856,11 +5855,12 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5883,99 +5883,99 @@
         <v>11</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="101" t="s">
+      <c r="D1" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="103"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="114"/>
     </row>
     <row r="2" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="105"/>
+      <c r="C2" s="122"/>
       <c r="D2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="104" t="s">
+      <c r="E2" s="107" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="107"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="111"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="103"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="114"/>
     </row>
     <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="19">
         <v>1</v>
       </c>
-      <c r="B4" s="98" t="s">
+      <c r="B4" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="100"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="120"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>2</v>
       </c>
-      <c r="B5" s="104" t="s">
+      <c r="B5" s="107" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="107"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="111"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="103"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="114"/>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="111" t="s">
+      <c r="A7" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="112"/>
-      <c r="C7" s="113"/>
-      <c r="D7" s="114" t="s">
+      <c r="B7" s="116"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="113"/>
+      <c r="E7" s="117"/>
       <c r="F7" s="50" t="s">
         <v>20</v>
       </c>
@@ -5990,54 +5990,54 @@
       <c r="A8" s="19">
         <v>1</v>
       </c>
-      <c r="B8" s="98" t="s">
+      <c r="B8" s="105" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="115"/>
-      <c r="D8" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E8" s="116"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" s="109"/>
       <c r="F8" s="46"/>
       <c r="G8" s="46" t="s">
         <v>96</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19">
         <v>2</v>
       </c>
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="115"/>
-      <c r="D9" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E9" s="116"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E9" s="109"/>
       <c r="F9" s="21"/>
       <c r="G9" s="46" t="s">
         <v>96</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E10" s="116"/>
+      <c r="C10" s="106"/>
+      <c r="D10" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" s="109"/>
       <c r="F10" s="46" t="s">
         <v>95</v>
       </c>
@@ -6048,14 +6048,14 @@
       <c r="A11" s="19">
         <v>4</v>
       </c>
-      <c r="B11" s="98" t="s">
+      <c r="B11" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="115"/>
-      <c r="D11" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E11" s="116"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E11" s="109"/>
       <c r="F11" s="46" t="s">
         <v>95</v>
       </c>
@@ -6066,14 +6066,14 @@
       <c r="A12" s="19">
         <v>5</v>
       </c>
-      <c r="B12" s="98" t="s">
+      <c r="B12" s="105" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="115"/>
-      <c r="D12" s="104" t="s">
-        <v>243</v>
-      </c>
-      <c r="E12" s="124"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="107" t="s">
+        <v>242</v>
+      </c>
+      <c r="E12" s="108"/>
       <c r="F12" s="46" t="s">
         <v>95</v>
       </c>
@@ -6084,14 +6084,14 @@
       <c r="A13" s="19">
         <v>6</v>
       </c>
-      <c r="B13" s="98" t="s">
-        <v>240</v>
-      </c>
-      <c r="C13" s="115"/>
-      <c r="D13" s="104" t="s">
-        <v>243</v>
-      </c>
-      <c r="E13" s="124"/>
+      <c r="B13" s="105" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" s="106"/>
+      <c r="D13" s="107" t="s">
+        <v>242</v>
+      </c>
+      <c r="E13" s="108"/>
       <c r="F13" s="46" t="s">
         <v>95</v>
       </c>
@@ -6102,14 +6102,14 @@
       <c r="A14" s="23">
         <v>7</v>
       </c>
-      <c r="B14" s="104" t="s">
+      <c r="B14" s="107" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="124"/>
-      <c r="D14" s="104" t="s">
-        <v>243</v>
-      </c>
-      <c r="E14" s="124"/>
+      <c r="C14" s="108"/>
+      <c r="D14" s="107" t="s">
+        <v>242</v>
+      </c>
+      <c r="E14" s="108"/>
       <c r="F14" s="46" t="s">
         <v>95</v>
       </c>
@@ -6117,25 +6117,43 @@
       <c r="H14" s="25"/>
     </row>
     <row r="15" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="117" t="s">
+      <c r="A15" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="118"/>
-      <c r="C15" s="119" t="s">
+      <c r="B15" s="99"/>
+      <c r="C15" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="120"/>
+      <c r="D15" s="101"/>
       <c r="E15" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="121">
+      <c r="F15" s="102">
         <v>46227</v>
       </c>
-      <c r="G15" s="122"/>
-      <c r="H15" s="123"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="F15:H15"/>
@@ -6145,24 +6163,6 @@
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="D14:E14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:H3"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6187,15 +6187,15 @@
         <v>98</v>
       </c>
       <c r="B1" s="47" t="s">
-        <v>152</v>
-      </c>
-      <c r="C1" s="130"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
+        <v>151</v>
+      </c>
+      <c r="C1" s="127"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="47" t="s">
@@ -6211,11 +6211,11 @@
       <c r="E2" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="126" t="s">
+      <c r="F2" s="129" t="s">
         <v>125</v>
       </c>
-      <c r="G2" s="132"/>
-      <c r="H2" s="133"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="131"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="47" t="s">
@@ -6233,32 +6233,32 @@
       <c r="E3" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="F3" s="126" t="s">
+      <c r="F3" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="G3" s="132"/>
-      <c r="H3" s="133"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="131"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="126" t="s">
+      <c r="B4" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="132"/>
-      <c r="D4" s="132"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="133"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="131"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="47" t="s">
         <v>107</v>
       </c>
       <c r="B5" s="125" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C5" s="125"/>
       <c r="D5" s="125"/>
@@ -6282,40 +6282,40 @@
       <c r="H6" s="125"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="129" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="128"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="133"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="129" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="127"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="127"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="127"/>
-      <c r="H8" s="128"/>
+      <c r="B8" s="132"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="133"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="129" t="s">
+      <c r="A9" s="126" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="129"/>
-      <c r="C9" s="129"/>
-      <c r="D9" s="129"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="129"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="129"/>
+      <c r="B9" s="126"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="126"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="126"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="47">
@@ -6346,16 +6346,16 @@
       <c r="H11" s="125"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="129" t="s">
+      <c r="A12" s="126" t="s">
         <v>109</v>
       </c>
-      <c r="B12" s="129"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
+      <c r="B12" s="126"/>
+      <c r="C12" s="126"/>
+      <c r="D12" s="126"/>
+      <c r="E12" s="126"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="126"/>
+      <c r="H12" s="126"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="47">
@@ -6422,16 +6422,16 @@
       <c r="H17" s="125"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="129" t="s">
+      <c r="A18" s="126" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="129"/>
-      <c r="C18" s="129"/>
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="129"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="126"/>
+      <c r="G18" s="126"/>
+      <c r="H18" s="126"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="125" t="s">
@@ -6468,16 +6468,16 @@
       <c r="H21" s="125"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="129" t="s">
+      <c r="A22" s="126" t="s">
         <v>123</v>
       </c>
-      <c r="B22" s="129"/>
-      <c r="C22" s="129"/>
-      <c r="D22" s="129"/>
-      <c r="E22" s="129"/>
-      <c r="F22" s="129"/>
-      <c r="G22" s="129"/>
-      <c r="H22" s="129"/>
+      <c r="B22" s="126"/>
+      <c r="C22" s="126"/>
+      <c r="D22" s="126"/>
+      <c r="E22" s="126"/>
+      <c r="F22" s="126"/>
+      <c r="G22" s="126"/>
+      <c r="H22" s="126"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="125" t="s">
@@ -6547,16 +6547,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B6:H6"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="A7:H7"/>
@@ -6573,6 +6563,16 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -6596,99 +6596,99 @@
         <v>11</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="101" t="s">
+      <c r="D1" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="103"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="114"/>
     </row>
     <row r="2" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="105"/>
+      <c r="C2" s="122"/>
       <c r="D2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="104" t="s">
+      <c r="E2" s="107" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="107"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="111"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="103"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="114"/>
     </row>
     <row r="4" spans="1:8" ht="15.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19">
         <v>1</v>
       </c>
-      <c r="B4" s="98" t="s">
+      <c r="B4" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="100"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="120"/>
     </row>
     <row r="5" spans="1:8" ht="16.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>2</v>
       </c>
-      <c r="B5" s="104" t="s">
+      <c r="B5" s="107" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="107"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="111"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="103"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="114"/>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="134" t="s">
+      <c r="A7" s="136" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="135" t="s">
+      <c r="B7" s="119"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="116"/>
+      <c r="E7" s="109"/>
       <c r="F7" s="21" t="s">
         <v>20</v>
       </c>
@@ -6703,14 +6703,14 @@
       <c r="A8" s="19">
         <v>1</v>
       </c>
-      <c r="B8" s="98" t="s">
+      <c r="B8" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="116"/>
-      <c r="D8" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E8" s="116"/>
+      <c r="C8" s="109"/>
+      <c r="D8" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" s="109"/>
       <c r="F8" s="46" t="s">
         <v>95</v>
       </c>
@@ -6721,14 +6721,14 @@
       <c r="A9" s="19">
         <v>2</v>
       </c>
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="116"/>
-      <c r="D9" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E9" s="116"/>
+      <c r="C9" s="109"/>
+      <c r="D9" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E9" s="109"/>
       <c r="F9" s="46" t="s">
         <v>95</v>
       </c>
@@ -6739,14 +6739,14 @@
       <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="116"/>
-      <c r="D10" s="98" t="s">
-        <v>243</v>
-      </c>
-      <c r="E10" s="116"/>
+      <c r="C10" s="109"/>
+      <c r="D10" s="105" t="s">
+        <v>242</v>
+      </c>
+      <c r="E10" s="109"/>
       <c r="F10" s="46" t="s">
         <v>95</v>
       </c>
@@ -6757,14 +6757,14 @@
       <c r="A11" s="19">
         <v>4</v>
       </c>
-      <c r="B11" s="98" t="s">
+      <c r="B11" s="105" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="116"/>
-      <c r="D11" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E11" s="116"/>
+      <c r="C11" s="109"/>
+      <c r="D11" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E11" s="109"/>
       <c r="F11" s="46" t="s">
         <v>95</v>
       </c>
@@ -6775,14 +6775,14 @@
       <c r="A12" s="19">
         <v>5</v>
       </c>
-      <c r="B12" s="98" t="s">
+      <c r="B12" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="116"/>
-      <c r="D12" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E12" s="116"/>
+      <c r="C12" s="109"/>
+      <c r="D12" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" s="109"/>
       <c r="F12" s="46" t="s">
         <v>95</v>
       </c>
@@ -6793,14 +6793,14 @@
       <c r="A13" s="19">
         <v>6</v>
       </c>
-      <c r="B13" s="98" t="s">
+      <c r="B13" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="116"/>
-      <c r="D13" s="98" t="s">
-        <v>243</v>
-      </c>
-      <c r="E13" s="116"/>
+      <c r="C13" s="109"/>
+      <c r="D13" s="105" t="s">
+        <v>242</v>
+      </c>
+      <c r="E13" s="109"/>
       <c r="F13" s="46" t="s">
         <v>95</v>
       </c>
@@ -6811,14 +6811,14 @@
       <c r="A14" s="23">
         <v>7</v>
       </c>
-      <c r="B14" s="98" t="s">
+      <c r="B14" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="115"/>
-      <c r="D14" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E14" s="116"/>
+      <c r="C14" s="106"/>
+      <c r="D14" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E14" s="109"/>
       <c r="F14" s="46" t="s">
         <v>95</v>
       </c>
@@ -6829,14 +6829,14 @@
       <c r="A15" s="23">
         <v>8</v>
       </c>
-      <c r="B15" s="98" t="s">
+      <c r="B15" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="115"/>
-      <c r="D15" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E15" s="116"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" s="109"/>
       <c r="F15" s="46" t="s">
         <v>95</v>
       </c>
@@ -6847,14 +6847,14 @@
       <c r="A16" s="23">
         <v>9</v>
       </c>
-      <c r="B16" s="136" t="s">
+      <c r="B16" s="134" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="137"/>
-      <c r="D16" s="104" t="s">
-        <v>243</v>
-      </c>
-      <c r="E16" s="124"/>
+      <c r="C16" s="135"/>
+      <c r="D16" s="107" t="s">
+        <v>242</v>
+      </c>
+      <c r="E16" s="108"/>
       <c r="F16" s="46" t="s">
         <v>95</v>
       </c>
@@ -6862,25 +6862,43 @@
       <c r="H16" s="25"/>
     </row>
     <row r="17" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="117" t="s">
+      <c r="A17" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="118"/>
-      <c r="C17" s="119" t="s">
+      <c r="B17" s="99"/>
+      <c r="C17" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="120"/>
+      <c r="D17" s="101"/>
       <c r="E17" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="121">
+      <c r="F17" s="102">
         <v>46227</v>
       </c>
-      <c r="G17" s="122"/>
-      <c r="H17" s="123"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="F17:H17"/>
@@ -6894,24 +6912,6 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D15:E15"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6929,18 +6929,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
       <c r="D1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="F1" s="89"/>
+      <c r="E1" s="88" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" s="88"/>
     </row>
     <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="33"/>
@@ -6950,18 +6950,18 @@
       <c r="E2" s="34"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="89" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="89"/>
+      <c r="A3" s="88" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="88"/>
       <c r="C3" s="31"/>
       <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="89" t="s">
+      <c r="E3" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="89"/>
+      <c r="F3" s="88"/>
     </row>
     <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
@@ -6971,44 +6971,44 @@
       <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="87" t="s">
+      <c r="A5" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="82" t="s">
+      <c r="B5" s="89"/>
+      <c r="C5" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
     </row>
     <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="87"/>
-      <c r="C6" s="82" t="s">
+      <c r="B6" s="89"/>
+      <c r="C6" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
     </row>
     <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="87"/>
-      <c r="C7" s="82" t="s">
+      <c r="B7" s="89"/>
+      <c r="C7" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
     </row>
     <row r="8" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="83"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="84"/>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
+      <c r="A8" s="91"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="92"/>
     </row>
     <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="32"/>
@@ -7018,19 +7018,19 @@
       <c r="E9" s="32"/>
     </row>
     <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
       <c r="D10" s="14"/>
       <c r="E10" s="32"/>
     </row>
     <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="86"/>
+      <c r="B11" s="94"/>
       <c r="C11" s="45" t="s">
         <v>95</v>
       </c>
@@ -7038,10 +7038,10 @@
       <c r="E11" s="32"/>
     </row>
     <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="86" t="s">
+      <c r="A12" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="86"/>
+      <c r="B12" s="94"/>
       <c r="C12" s="45" t="s">
         <v>95</v>
       </c>
@@ -7049,10 +7049,10 @@
       <c r="E12" s="32"/>
     </row>
     <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="86"/>
+      <c r="B13" s="94"/>
       <c r="C13" s="45" t="s">
         <v>95</v>
       </c>
@@ -7063,7 +7063,7 @@
       <c r="A14" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="94"/>
+      <c r="B14" s="86"/>
       <c r="C14" s="45" t="s">
         <v>95</v>
       </c>
@@ -7071,10 +7071,10 @@
       <c r="E14" s="32"/>
     </row>
     <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="86" t="s">
+      <c r="A15" s="94" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="86"/>
+      <c r="B15" s="94"/>
       <c r="C15" s="45" t="s">
         <v>95</v>
       </c>
@@ -7082,10 +7082,10 @@
       <c r="E15" s="32"/>
     </row>
     <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="86" t="s">
+      <c r="A16" s="94" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="86"/>
+      <c r="B16" s="94"/>
       <c r="C16" s="45" t="s">
         <v>95</v>
       </c>
@@ -7094,6 +7094,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="A10:C10"/>
@@ -7102,17 +7113,6 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A8:B8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7135,99 +7135,99 @@
         <v>11</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="101" t="s">
+      <c r="D1" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="103"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="114"/>
     </row>
     <row r="2" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="105"/>
+      <c r="C2" s="122"/>
       <c r="D2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="104" t="s">
+      <c r="E2" s="107" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="107"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="111"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="103"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="114"/>
     </row>
     <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="19">
         <v>1</v>
       </c>
-      <c r="B4" s="98" t="s">
+      <c r="B4" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="100"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="120"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>2</v>
       </c>
-      <c r="B5" s="104" t="s">
+      <c r="B5" s="107" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="107"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="111"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="103"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="114"/>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="134" t="s">
+      <c r="A7" s="136" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="135" t="s">
+      <c r="B7" s="119"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="116"/>
+      <c r="E7" s="109"/>
       <c r="F7" s="21" t="s">
         <v>20</v>
       </c>
@@ -7242,14 +7242,14 @@
       <c r="A8" s="19">
         <v>1</v>
       </c>
-      <c r="B8" s="98" t="s">
+      <c r="B8" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="115"/>
-      <c r="D8" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E8" s="116"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" s="109"/>
       <c r="F8" s="46" t="s">
         <v>95</v>
       </c>
@@ -7260,14 +7260,14 @@
       <c r="A9" s="19">
         <v>2</v>
       </c>
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="115"/>
-      <c r="D9" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E9" s="116"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E9" s="109"/>
       <c r="F9" s="46" t="s">
         <v>95</v>
       </c>
@@ -7278,14 +7278,14 @@
       <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E10" s="116"/>
+      <c r="C10" s="106"/>
+      <c r="D10" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" s="109"/>
       <c r="F10" s="46" t="s">
         <v>95</v>
       </c>
@@ -7296,14 +7296,14 @@
       <c r="A11" s="19">
         <v>4</v>
       </c>
-      <c r="B11" s="98" t="s">
+      <c r="B11" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="115"/>
-      <c r="D11" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E11" s="116"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E11" s="109"/>
       <c r="F11" s="46" t="s">
         <v>95</v>
       </c>
@@ -7314,14 +7314,14 @@
       <c r="A12" s="19">
         <v>5</v>
       </c>
-      <c r="B12" s="98" t="s">
+      <c r="B12" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="115"/>
-      <c r="D12" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E12" s="116"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" s="109"/>
       <c r="F12" s="46" t="s">
         <v>95</v>
       </c>
@@ -7332,14 +7332,14 @@
       <c r="A13" s="19">
         <v>6</v>
       </c>
-      <c r="B13" s="98" t="s">
+      <c r="B13" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="115"/>
-      <c r="D13" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E13" s="116"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E13" s="109"/>
       <c r="F13" s="46" t="s">
         <v>95</v>
       </c>
@@ -7350,14 +7350,14 @@
       <c r="A14" s="23">
         <v>7</v>
       </c>
-      <c r="B14" s="98" t="s">
+      <c r="B14" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="115"/>
-      <c r="D14" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E14" s="116"/>
+      <c r="C14" s="106"/>
+      <c r="D14" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E14" s="109"/>
       <c r="F14" s="46" t="s">
         <v>95</v>
       </c>
@@ -7368,14 +7368,14 @@
       <c r="A15" s="23">
         <v>8</v>
       </c>
-      <c r="B15" s="98" t="s">
+      <c r="B15" s="105" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="115"/>
-      <c r="D15" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E15" s="116"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" s="109"/>
       <c r="F15" s="46" t="s">
         <v>95</v>
       </c>
@@ -7386,14 +7386,14 @@
       <c r="A16" s="23">
         <v>9</v>
       </c>
-      <c r="B16" s="104" t="s">
-        <v>210</v>
-      </c>
-      <c r="C16" s="124"/>
-      <c r="D16" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="E16" s="116"/>
+      <c r="B16" s="107" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="E16" s="109"/>
       <c r="F16" s="46" t="s">
         <v>95</v>
       </c>
@@ -7401,14 +7401,14 @@
       <c r="H16" s="25"/>
     </row>
     <row r="17" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="117" t="s">
+      <c r="A17" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="118"/>
-      <c r="C17" s="119" t="s">
+      <c r="B17" s="99"/>
+      <c r="C17" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="120"/>
+      <c r="D17" s="101"/>
       <c r="E17" s="26" t="s">
         <v>24</v>
       </c>
@@ -7421,6 +7421,30 @@
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="F17:H17"/>
@@ -7428,30 +7452,6 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D15:E15"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7475,97 +7475,97 @@
         <v>11</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="101" t="s">
+      <c r="D1" s="121" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="103"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="114"/>
     </row>
     <row r="2" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="105"/>
+      <c r="C2" s="122"/>
       <c r="D2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="104" t="s">
+      <c r="E2" s="107" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="107"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="111"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="103"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="114"/>
     </row>
     <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="19">
         <v>1</v>
       </c>
-      <c r="B4" s="98" t="s">
+      <c r="B4" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="100"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="120"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>2</v>
       </c>
-      <c r="B5" s="104"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="107"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="111"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="103"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="114"/>
     </row>
     <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.35">
-      <c r="A7" s="134" t="s">
+      <c r="A7" s="136" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="135" t="s">
+      <c r="B7" s="119"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="116"/>
+      <c r="E7" s="109"/>
       <c r="F7" s="21" t="s">
         <v>20</v>
       </c>
@@ -7580,14 +7580,14 @@
       <c r="A8" s="19">
         <v>1</v>
       </c>
-      <c r="B8" s="98" t="s">
-        <v>232</v>
-      </c>
-      <c r="C8" s="116"/>
-      <c r="D8" s="98" t="s">
-        <v>236</v>
-      </c>
-      <c r="E8" s="116"/>
+      <c r="B8" s="105" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" s="109"/>
+      <c r="D8" s="105" t="s">
+        <v>235</v>
+      </c>
+      <c r="E8" s="109"/>
       <c r="F8" s="46" t="s">
         <v>95</v>
       </c>
@@ -7598,14 +7598,14 @@
       <c r="A9" s="19">
         <v>2</v>
       </c>
-      <c r="B9" s="98" t="s">
-        <v>233</v>
-      </c>
-      <c r="C9" s="116"/>
-      <c r="D9" s="98" t="s">
-        <v>237</v>
-      </c>
-      <c r="E9" s="116"/>
+      <c r="B9" s="105" t="s">
+        <v>232</v>
+      </c>
+      <c r="C9" s="109"/>
+      <c r="D9" s="105" t="s">
+        <v>236</v>
+      </c>
+      <c r="E9" s="109"/>
       <c r="F9" s="46" t="s">
         <v>95</v>
       </c>
@@ -7616,14 +7616,14 @@
       <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="98" t="s">
-        <v>234</v>
-      </c>
-      <c r="C10" s="116"/>
-      <c r="D10" s="98" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10" s="116"/>
+      <c r="B10" s="105" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="109"/>
+      <c r="D10" s="105" t="s">
+        <v>235</v>
+      </c>
+      <c r="E10" s="109"/>
       <c r="F10" s="46" t="s">
         <v>95</v>
       </c>
@@ -7634,14 +7634,14 @@
       <c r="A11" s="19">
         <v>4</v>
       </c>
-      <c r="B11" s="98" t="s">
-        <v>235</v>
-      </c>
-      <c r="C11" s="116"/>
-      <c r="D11" s="98" t="s">
-        <v>238</v>
-      </c>
-      <c r="E11" s="116"/>
+      <c r="B11" s="105" t="s">
+        <v>234</v>
+      </c>
+      <c r="C11" s="109"/>
+      <c r="D11" s="105" t="s">
+        <v>237</v>
+      </c>
+      <c r="E11" s="109"/>
       <c r="F11" s="46" t="s">
         <v>95</v>
       </c>
@@ -7652,10 +7652,10 @@
       <c r="A12" s="19">
         <v>5</v>
       </c>
-      <c r="B12" s="98"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="116"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="109"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="109"/>
       <c r="F12" s="21"/>
       <c r="G12" s="21"/>
       <c r="H12" s="22"/>
@@ -7664,10 +7664,10 @@
       <c r="A13" s="19">
         <v>6</v>
       </c>
-      <c r="B13" s="98"/>
-      <c r="C13" s="116"/>
-      <c r="D13" s="98"/>
-      <c r="E13" s="116"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="109"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="109"/>
       <c r="F13" s="21"/>
       <c r="G13" s="21"/>
       <c r="H13" s="22"/>
@@ -7676,23 +7676,23 @@
       <c r="A14" s="23">
         <v>7</v>
       </c>
-      <c r="B14" s="136"/>
-      <c r="C14" s="137"/>
-      <c r="D14" s="136"/>
-      <c r="E14" s="137"/>
+      <c r="B14" s="134"/>
+      <c r="C14" s="135"/>
+      <c r="D14" s="134"/>
+      <c r="E14" s="135"/>
       <c r="F14" s="24"/>
       <c r="G14" s="24"/>
       <c r="H14" s="25"/>
     </row>
     <row r="15" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="117" t="s">
+      <c r="A15" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="118"/>
-      <c r="C15" s="119" t="s">
+      <c r="B15" s="99"/>
+      <c r="C15" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="120"/>
+      <c r="D15" s="101"/>
       <c r="E15" s="26" t="s">
         <v>24</v>
       </c>
@@ -7704,6 +7704,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="F15:H15"/>
@@ -7713,24 +7731,6 @@
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="D14:E14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
